--- a/output/version3/test/10-5/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>434</v>
+        <v>524</v>
       </c>
       <c r="C2" t="n">
-        <v>456</v>
+        <v>547</v>
       </c>
       <c r="D2" t="n">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="E2" t="n">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="F2" t="n">
-        <v>610</v>
+        <v>413</v>
       </c>
       <c r="G2" t="n">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="H2" t="n">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="I2" t="n">
-        <v>493</v>
+        <v>458</v>
       </c>
       <c r="J2" t="n">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K2" t="n">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="L2" t="n">
-        <v>474.8</v>
+        <v>474.1</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C3" t="n">
-        <v>574</v>
+        <v>514</v>
       </c>
       <c r="D3" t="n">
-        <v>478</v>
+        <v>513</v>
       </c>
       <c r="E3" t="n">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F3" t="n">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="G3" t="n">
-        <v>474</v>
+        <v>568</v>
       </c>
       <c r="H3" t="n">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="I3" t="n">
-        <v>538</v>
+        <v>483</v>
       </c>
       <c r="J3" t="n">
-        <v>477</v>
+        <v>529</v>
       </c>
       <c r="K3" t="n">
-        <v>549</v>
+        <v>465</v>
       </c>
       <c r="L3" t="n">
-        <v>512.1</v>
+        <v>510.1</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>539</v>
+        <v>514</v>
       </c>
       <c r="C4" t="n">
-        <v>592</v>
+        <v>636</v>
       </c>
       <c r="D4" t="n">
-        <v>454</v>
+        <v>514</v>
       </c>
       <c r="E4" t="n">
-        <v>477</v>
+        <v>593</v>
       </c>
       <c r="F4" t="n">
-        <v>513</v>
+        <v>557</v>
       </c>
       <c r="G4" t="n">
-        <v>515</v>
+        <v>540</v>
       </c>
       <c r="H4" t="n">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="I4" t="n">
+        <v>529</v>
+      </c>
+      <c r="J4" t="n">
+        <v>535</v>
+      </c>
+      <c r="K4" t="n">
         <v>502</v>
       </c>
-      <c r="J4" t="n">
-        <v>467</v>
-      </c>
-      <c r="K4" t="n">
-        <v>625</v>
-      </c>
       <c r="L4" t="n">
-        <v>518.3</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="C5" t="n">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="D5" t="n">
-        <v>457</v>
+        <v>535</v>
       </c>
       <c r="E5" t="n">
-        <v>476</v>
+        <v>532</v>
       </c>
       <c r="F5" t="n">
-        <v>439</v>
+        <v>555</v>
       </c>
       <c r="G5" t="n">
-        <v>472</v>
+        <v>527</v>
       </c>
       <c r="H5" t="n">
-        <v>453</v>
+        <v>500</v>
       </c>
       <c r="I5" t="n">
-        <v>516</v>
+        <v>491</v>
       </c>
       <c r="J5" t="n">
-        <v>462</v>
+        <v>539</v>
       </c>
       <c r="K5" t="n">
-        <v>450</v>
+        <v>519</v>
       </c>
       <c r="L5" t="n">
-        <v>457.8</v>
+        <v>513.4</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="C6" t="n">
-        <v>503</v>
+        <v>465</v>
       </c>
       <c r="D6" t="n">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="E6" t="n">
-        <v>493</v>
+        <v>447</v>
       </c>
       <c r="F6" t="n">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="G6" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="H6" t="n">
-        <v>451</v>
+        <v>554</v>
       </c>
       <c r="I6" t="n">
-        <v>465</v>
+        <v>498</v>
       </c>
       <c r="J6" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>499</v>
       </c>
       <c r="L6" t="n">
-        <v>463.2</v>
+        <v>473.3</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="C7" t="n">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="D7" t="n">
+        <v>474</v>
+      </c>
+      <c r="E7" t="n">
+        <v>467</v>
+      </c>
+      <c r="F7" t="n">
+        <v>444</v>
+      </c>
+      <c r="G7" t="n">
+        <v>438</v>
+      </c>
+      <c r="H7" t="n">
+        <v>470</v>
+      </c>
+      <c r="I7" t="n">
+        <v>447</v>
+      </c>
+      <c r="J7" t="n">
         <v>457</v>
       </c>
-      <c r="E7" t="n">
-        <v>449</v>
-      </c>
-      <c r="F7" t="n">
-        <v>524</v>
-      </c>
-      <c r="G7" t="n">
-        <v>525</v>
-      </c>
-      <c r="H7" t="n">
-        <v>419</v>
-      </c>
-      <c r="I7" t="n">
-        <v>454</v>
-      </c>
-      <c r="J7" t="n">
-        <v>403</v>
-      </c>
       <c r="K7" t="n">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="L7" t="n">
-        <v>475.9</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>456</v>
+        <v>526</v>
       </c>
       <c r="C8" t="n">
-        <v>501</v>
+        <v>558</v>
       </c>
       <c r="D8" t="n">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="E8" t="n">
-        <v>475</v>
+        <v>447</v>
       </c>
       <c r="F8" t="n">
-        <v>492</v>
+        <v>543</v>
       </c>
       <c r="G8" t="n">
-        <v>524</v>
+        <v>636</v>
       </c>
       <c r="H8" t="n">
-        <v>432</v>
+        <v>536</v>
       </c>
       <c r="I8" t="n">
-        <v>492</v>
+        <v>545</v>
       </c>
       <c r="J8" t="n">
-        <v>494</v>
+        <v>453</v>
       </c>
       <c r="K8" t="n">
-        <v>506</v>
+        <v>473</v>
       </c>
       <c r="L8" t="n">
-        <v>488.8</v>
+        <v>521.1</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C9" t="n">
-        <v>454</v>
+        <v>559</v>
       </c>
       <c r="D9" t="n">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="E9" t="n">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="F9" t="n">
-        <v>429</v>
+        <v>536</v>
       </c>
       <c r="G9" t="n">
-        <v>417</v>
+        <v>466</v>
       </c>
       <c r="H9" t="n">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="I9" t="n">
-        <v>455</v>
+        <v>527</v>
       </c>
       <c r="J9" t="n">
-        <v>446</v>
+        <v>488</v>
       </c>
       <c r="K9" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L9" t="n">
-        <v>453.9</v>
+        <v>495.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>503</v>
+        <v>443</v>
       </c>
       <c r="C10" t="n">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="D10" t="n">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="E10" t="n">
-        <v>558</v>
+        <v>524</v>
       </c>
       <c r="F10" t="n">
-        <v>481</v>
+        <v>446</v>
       </c>
       <c r="G10" t="n">
-        <v>540</v>
+        <v>482</v>
       </c>
       <c r="H10" t="n">
-        <v>495</v>
+        <v>455</v>
       </c>
       <c r="I10" t="n">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="J10" t="n">
-        <v>528</v>
+        <v>477</v>
       </c>
       <c r="K10" t="n">
-        <v>520</v>
+        <v>462</v>
       </c>
       <c r="L10" t="n">
-        <v>508.9</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>453</v>
+        <v>377</v>
       </c>
       <c r="C11" t="n">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="D11" t="n">
-        <v>495</v>
+        <v>433</v>
       </c>
       <c r="E11" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F11" t="n">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="G11" t="n">
-        <v>568</v>
+        <v>436</v>
       </c>
       <c r="H11" t="n">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="I11" t="n">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="J11" t="n">
-        <v>501</v>
+        <v>465</v>
       </c>
       <c r="K11" t="n">
-        <v>424</v>
+        <v>377</v>
       </c>
       <c r="L11" t="n">
-        <v>465.2</v>
+        <v>434.2</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C12" t="n">
-        <v>547</v>
+        <v>479</v>
       </c>
       <c r="D12" t="n">
-        <v>597</v>
+        <v>493</v>
       </c>
       <c r="E12" t="n">
-        <v>584</v>
+        <v>457</v>
       </c>
       <c r="F12" t="n">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="G12" t="n">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="H12" t="n">
-        <v>562</v>
+        <v>471</v>
       </c>
       <c r="I12" t="n">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="J12" t="n">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="K12" t="n">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="L12" t="n">
-        <v>534.2</v>
+        <v>493.5</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>587</v>
+        <v>532</v>
       </c>
       <c r="C13" t="n">
-        <v>534</v>
+        <v>482</v>
       </c>
       <c r="D13" t="n">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="E13" t="n">
+        <v>513</v>
+      </c>
+      <c r="F13" t="n">
         <v>512</v>
       </c>
-      <c r="F13" t="n">
-        <v>563</v>
-      </c>
       <c r="G13" t="n">
-        <v>580</v>
+        <v>524</v>
       </c>
       <c r="H13" t="n">
-        <v>547</v>
+        <v>564</v>
       </c>
       <c r="I13" t="n">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="J13" t="n">
-        <v>539</v>
+        <v>506</v>
       </c>
       <c r="K13" t="n">
-        <v>529</v>
+        <v>590</v>
       </c>
       <c r="L13" t="n">
-        <v>534.8</v>
+        <v>516.4</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>523</v>
+        <v>557</v>
       </c>
       <c r="C14" t="n">
-        <v>485</v>
+        <v>542</v>
       </c>
       <c r="D14" t="n">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="E14" t="n">
-        <v>482</v>
+        <v>559</v>
       </c>
       <c r="F14" t="n">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="G14" t="n">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="H14" t="n">
-        <v>571</v>
+        <v>545</v>
       </c>
       <c r="I14" t="n">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="J14" t="n">
-        <v>506</v>
+        <v>553</v>
       </c>
       <c r="K14" t="n">
-        <v>504</v>
+        <v>535</v>
       </c>
       <c r="L14" t="n">
-        <v>517.2</v>
+        <v>540.4</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
+        <v>515</v>
+      </c>
+      <c r="C15" t="n">
+        <v>455</v>
+      </c>
+      <c r="D15" t="n">
+        <v>436</v>
+      </c>
+      <c r="E15" t="n">
+        <v>485</v>
+      </c>
+      <c r="F15" t="n">
+        <v>482</v>
+      </c>
+      <c r="G15" t="n">
+        <v>514</v>
+      </c>
+      <c r="H15" t="n">
+        <v>514</v>
+      </c>
+      <c r="I15" t="n">
         <v>488</v>
       </c>
-      <c r="C15" t="n">
-        <v>482</v>
-      </c>
-      <c r="D15" t="n">
-        <v>488</v>
-      </c>
-      <c r="E15" t="n">
-        <v>479</v>
-      </c>
-      <c r="F15" t="n">
-        <v>498</v>
-      </c>
-      <c r="G15" t="n">
-        <v>473</v>
-      </c>
-      <c r="H15" t="n">
-        <v>500</v>
-      </c>
-      <c r="I15" t="n">
-        <v>505</v>
-      </c>
       <c r="J15" t="n">
-        <v>512</v>
+        <v>462</v>
       </c>
       <c r="K15" t="n">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="L15" t="n">
-        <v>486.3</v>
+        <v>482.6</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
+        <v>459</v>
+      </c>
+      <c r="C16" t="n">
+        <v>497</v>
+      </c>
+      <c r="D16" t="n">
+        <v>557</v>
+      </c>
+      <c r="E16" t="n">
+        <v>523</v>
+      </c>
+      <c r="F16" t="n">
+        <v>505</v>
+      </c>
+      <c r="G16" t="n">
+        <v>499</v>
+      </c>
+      <c r="H16" t="n">
+        <v>518</v>
+      </c>
+      <c r="I16" t="n">
         <v>492</v>
       </c>
-      <c r="C16" t="n">
-        <v>445</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="J16" t="n">
         <v>508</v>
       </c>
-      <c r="E16" t="n">
-        <v>476</v>
-      </c>
-      <c r="F16" t="n">
-        <v>468</v>
-      </c>
-      <c r="G16" t="n">
-        <v>479</v>
-      </c>
-      <c r="H16" t="n">
-        <v>533</v>
-      </c>
-      <c r="I16" t="n">
-        <v>466</v>
-      </c>
-      <c r="J16" t="n">
-        <v>524</v>
-      </c>
       <c r="K16" t="n">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="L16" t="n">
-        <v>489.4</v>
+        <v>504.3</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="C17" t="n">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="D17" t="n">
-        <v>459</v>
+        <v>427</v>
       </c>
       <c r="E17" t="n">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F17" t="n">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="G17" t="n">
-        <v>427</v>
+        <v>533</v>
       </c>
       <c r="H17" t="n">
-        <v>551</v>
+        <v>478</v>
       </c>
       <c r="I17" t="n">
-        <v>508</v>
+        <v>464</v>
       </c>
       <c r="J17" t="n">
-        <v>405</v>
+        <v>462</v>
       </c>
       <c r="K17" t="n">
-        <v>518</v>
+        <v>470</v>
       </c>
       <c r="L17" t="n">
-        <v>471.8</v>
+        <v>469.7</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>595</v>
+        <v>553</v>
       </c>
       <c r="C18" t="n">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="D18" t="n">
-        <v>493</v>
+        <v>548</v>
       </c>
       <c r="E18" t="n">
-        <v>515</v>
+        <v>546</v>
       </c>
       <c r="F18" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G18" t="n">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="H18" t="n">
-        <v>528</v>
+        <v>476</v>
       </c>
       <c r="I18" t="n">
-        <v>475</v>
+        <v>535</v>
       </c>
       <c r="J18" t="n">
-        <v>545</v>
+        <v>466</v>
       </c>
       <c r="K18" t="n">
-        <v>577</v>
+        <v>537</v>
       </c>
       <c r="L18" t="n">
-        <v>531.4</v>
+        <v>523.1</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>477</v>
+        <v>520</v>
       </c>
       <c r="C19" t="n">
         <v>527</v>
       </c>
       <c r="D19" t="n">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="E19" t="n">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="F19" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G19" t="n">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="H19" t="n">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="I19" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="J19" t="n">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="K19" t="n">
-        <v>500</v>
+        <v>554</v>
       </c>
       <c r="L19" t="n">
-        <v>507.6</v>
+        <v>524</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>510</v>
+        <v>453</v>
       </c>
       <c r="C20" t="n">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="D20" t="n">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="E20" t="n">
-        <v>455</v>
+        <v>588</v>
       </c>
       <c r="F20" t="n">
-        <v>514</v>
+        <v>477</v>
       </c>
       <c r="G20" t="n">
+        <v>445</v>
+      </c>
+      <c r="H20" t="n">
+        <v>581</v>
+      </c>
+      <c r="I20" t="n">
         <v>486</v>
       </c>
-      <c r="H20" t="n">
-        <v>551</v>
-      </c>
-      <c r="I20" t="n">
-        <v>485</v>
-      </c>
       <c r="J20" t="n">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="K20" t="n">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="L20" t="n">
-        <v>490.5</v>
+        <v>496.1</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="C21" t="n">
-        <v>477</v>
+        <v>437</v>
       </c>
       <c r="D21" t="n">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="E21" t="n">
-        <v>493</v>
+        <v>454</v>
       </c>
       <c r="F21" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="G21" t="n">
-        <v>493</v>
+        <v>443</v>
       </c>
       <c r="H21" t="n">
-        <v>571</v>
+        <v>495</v>
       </c>
       <c r="I21" t="n">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="J21" t="n">
-        <v>490</v>
+        <v>432</v>
       </c>
       <c r="K21" t="n">
-        <v>436</v>
+        <v>505</v>
       </c>
       <c r="L21" t="n">
-        <v>494.3</v>
+        <v>479.3</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>466</v>
+        <v>560</v>
       </c>
       <c r="C22" t="n">
-        <v>510</v>
+        <v>482</v>
       </c>
       <c r="D22" t="n">
-        <v>551</v>
+        <v>523</v>
       </c>
       <c r="E22" t="n">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="F22" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G22" t="n">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="H22" t="n">
-        <v>477</v>
+        <v>583</v>
       </c>
       <c r="I22" t="n">
-        <v>513</v>
+        <v>552</v>
       </c>
       <c r="J22" t="n">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="K22" t="n">
-        <v>493</v>
+        <v>546</v>
       </c>
       <c r="L22" t="n">
-        <v>504</v>
+        <v>528.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>469</v>
+        <v>397</v>
       </c>
       <c r="C23" t="n">
         <v>448</v>
       </c>
       <c r="D23" t="n">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="E23" t="n">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="F23" t="n">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="G23" t="n">
-        <v>374</v>
+        <v>448</v>
       </c>
       <c r="H23" t="n">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="I23" t="n">
-        <v>476</v>
+        <v>443</v>
       </c>
       <c r="J23" t="n">
-        <v>415</v>
+        <v>456</v>
       </c>
       <c r="K23" t="n">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="L23" t="n">
-        <v>437.7</v>
+        <v>446.2</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C24" t="n">
-        <v>516</v>
+        <v>454</v>
       </c>
       <c r="D24" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E24" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F24" t="n">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="G24" t="n">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="H24" t="n">
-        <v>571</v>
+        <v>451</v>
       </c>
       <c r="I24" t="n">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J24" t="n">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="K24" t="n">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="L24" t="n">
-        <v>452.8</v>
+        <v>438.6</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="C25" t="n">
-        <v>468</v>
+        <v>499</v>
       </c>
       <c r="D25" t="n">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="E25" t="n">
-        <v>419</v>
+        <v>475</v>
       </c>
       <c r="F25" t="n">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="G25" t="n">
-        <v>401</v>
+        <v>484</v>
       </c>
       <c r="H25" t="n">
+        <v>386</v>
+      </c>
+      <c r="I25" t="n">
         <v>403</v>
       </c>
-      <c r="I25" t="n">
-        <v>419</v>
-      </c>
       <c r="J25" t="n">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="K25" t="n">
-        <v>447</v>
+        <v>386</v>
       </c>
       <c r="L25" t="n">
-        <v>420</v>
+        <v>434.1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>522</v>
+        <v>572</v>
       </c>
       <c r="C26" t="n">
+        <v>589</v>
+      </c>
+      <c r="D26" t="n">
+        <v>563</v>
+      </c>
+      <c r="E26" t="n">
+        <v>495</v>
+      </c>
+      <c r="F26" t="n">
+        <v>558</v>
+      </c>
+      <c r="G26" t="n">
+        <v>563</v>
+      </c>
+      <c r="H26" t="n">
+        <v>504</v>
+      </c>
+      <c r="I26" t="n">
         <v>532</v>
       </c>
-      <c r="D26" t="n">
-        <v>535</v>
-      </c>
-      <c r="E26" t="n">
-        <v>476</v>
-      </c>
-      <c r="F26" t="n">
-        <v>553</v>
-      </c>
-      <c r="G26" t="n">
-        <v>562</v>
-      </c>
-      <c r="H26" t="n">
-        <v>619</v>
-      </c>
-      <c r="I26" t="n">
-        <v>561</v>
-      </c>
       <c r="J26" t="n">
+        <v>540</v>
+      </c>
+      <c r="K26" t="n">
         <v>541</v>
       </c>
-      <c r="K26" t="n">
-        <v>597</v>
-      </c>
       <c r="L26" t="n">
-        <v>549.8</v>
+        <v>545.7</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>404</v>
+        <v>448</v>
       </c>
       <c r="C27" t="n">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="D27" t="n">
+        <v>457</v>
+      </c>
+      <c r="E27" t="n">
+        <v>458</v>
+      </c>
+      <c r="F27" t="n">
+        <v>421</v>
+      </c>
+      <c r="G27" t="n">
+        <v>436</v>
+      </c>
+      <c r="H27" t="n">
         <v>434</v>
       </c>
-      <c r="E27" t="n">
-        <v>446</v>
-      </c>
-      <c r="F27" t="n">
-        <v>456</v>
-      </c>
-      <c r="G27" t="n">
-        <v>489</v>
-      </c>
-      <c r="H27" t="n">
-        <v>435</v>
-      </c>
       <c r="I27" t="n">
+        <v>389</v>
+      </c>
+      <c r="J27" t="n">
         <v>444</v>
       </c>
-      <c r="J27" t="n">
-        <v>474</v>
-      </c>
       <c r="K27" t="n">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="L27" t="n">
-        <v>450.4</v>
+        <v>439.3</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>433</v>
+        <v>512</v>
       </c>
       <c r="C28" t="n">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="D28" t="n">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E28" t="n">
-        <v>492</v>
+        <v>440</v>
       </c>
       <c r="F28" t="n">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="G28" t="n">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="H28" t="n">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="I28" t="n">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="J28" t="n">
-        <v>478</v>
+        <v>436</v>
       </c>
       <c r="K28" t="n">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="L28" t="n">
-        <v>467.6</v>
+        <v>467.3</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="C29" t="n">
         <v>415</v>
       </c>
       <c r="D29" t="n">
-        <v>460</v>
+        <v>419</v>
       </c>
       <c r="E29" t="n">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="F29" t="n">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="G29" t="n">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="H29" t="n">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="I29" t="n">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="J29" t="n">
-        <v>450</v>
+        <v>496</v>
       </c>
       <c r="K29" t="n">
-        <v>454</v>
+        <v>415</v>
       </c>
       <c r="L29" t="n">
-        <v>451.6</v>
+        <v>443.9</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="C30" t="n">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="D30" t="n">
-        <v>482</v>
+        <v>581</v>
       </c>
       <c r="E30" t="n">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="F30" t="n">
-        <v>442</v>
+        <v>492</v>
       </c>
       <c r="G30" t="n">
-        <v>380</v>
+        <v>441</v>
       </c>
       <c r="H30" t="n">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="I30" t="n">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="J30" t="n">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="K30" t="n">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="L30" t="n">
-        <v>450</v>
+        <v>467.4</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="C31" t="n">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="D31" t="n">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="E31" t="n">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="F31" t="n">
+        <v>466</v>
+      </c>
+      <c r="G31" t="n">
+        <v>477</v>
+      </c>
+      <c r="H31" t="n">
+        <v>444</v>
+      </c>
+      <c r="I31" t="n">
         <v>449</v>
-      </c>
-      <c r="G31" t="n">
-        <v>475</v>
-      </c>
-      <c r="H31" t="n">
-        <v>458</v>
-      </c>
-      <c r="I31" t="n">
-        <v>462</v>
       </c>
       <c r="J31" t="n">
         <v>444</v>
       </c>
       <c r="K31" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="L31" t="n">
-        <v>459.5</v>
+        <v>455.6</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C32" t="n">
+        <v>422</v>
+      </c>
+      <c r="D32" t="n">
+        <v>410</v>
+      </c>
+      <c r="E32" t="n">
+        <v>481</v>
+      </c>
+      <c r="F32" t="n">
+        <v>450</v>
+      </c>
+      <c r="G32" t="n">
         <v>438</v>
       </c>
-      <c r="D32" t="n">
-        <v>443</v>
-      </c>
-      <c r="E32" t="n">
-        <v>425</v>
-      </c>
-      <c r="F32" t="n">
-        <v>409</v>
-      </c>
-      <c r="G32" t="n">
-        <v>398</v>
-      </c>
       <c r="H32" t="n">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="I32" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J32" t="n">
-        <v>575</v>
+        <v>420</v>
       </c>
       <c r="K32" t="n">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="L32" t="n">
-        <v>441.5</v>
+        <v>431.6</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>453</v>
+        <v>550</v>
       </c>
       <c r="C33" t="n">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="D33" t="n">
-        <v>478</v>
+        <v>449</v>
       </c>
       <c r="E33" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F33" t="n">
-        <v>468</v>
+        <v>422</v>
       </c>
       <c r="G33" t="n">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="H33" t="n">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="I33" t="n">
-        <v>475</v>
+        <v>404</v>
       </c>
       <c r="J33" t="n">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="K33" t="n">
-        <v>414</v>
+        <v>474</v>
       </c>
       <c r="L33" t="n">
-        <v>443.5</v>
+        <v>452.3</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="C34" t="n">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="D34" t="n">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="E34" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F34" t="n">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="G34" t="n">
-        <v>440</v>
+        <v>381</v>
       </c>
       <c r="H34" t="n">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="I34" t="n">
-        <v>433</v>
+        <v>462</v>
       </c>
       <c r="J34" t="n">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="K34" t="n">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="L34" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>523</v>
+        <v>477</v>
       </c>
       <c r="C35" t="n">
-        <v>574</v>
+        <v>492</v>
       </c>
       <c r="D35" t="n">
+        <v>502</v>
+      </c>
+      <c r="E35" t="n">
         <v>491</v>
       </c>
-      <c r="E35" t="n">
-        <v>550</v>
-      </c>
       <c r="F35" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="G35" t="n">
-        <v>479</v>
+        <v>388</v>
       </c>
       <c r="H35" t="n">
-        <v>577</v>
+        <v>510</v>
       </c>
       <c r="I35" t="n">
-        <v>539</v>
+        <v>503</v>
       </c>
       <c r="J35" t="n">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="K35" t="n">
-        <v>474</v>
+        <v>434</v>
       </c>
       <c r="L35" t="n">
-        <v>514.5</v>
+        <v>475.1</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="C36" t="n">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="D36" t="n">
-        <v>351</v>
+        <v>431</v>
       </c>
       <c r="E36" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F36" t="n">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="G36" t="n">
-        <v>343</v>
+        <v>407</v>
       </c>
       <c r="H36" t="n">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="I36" t="n">
-        <v>387</v>
+        <v>453</v>
       </c>
       <c r="J36" t="n">
-        <v>337</v>
+        <v>392</v>
       </c>
       <c r="K36" t="n">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="L36" t="n">
-        <v>382.2</v>
+        <v>418.4</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>497</v>
+        <v>432</v>
       </c>
       <c r="C37" t="n">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="D37" t="n">
-        <v>441</v>
+        <v>481</v>
       </c>
       <c r="E37" t="n">
-        <v>520</v>
+        <v>492</v>
       </c>
       <c r="F37" t="n">
-        <v>507</v>
+        <v>470</v>
       </c>
       <c r="G37" t="n">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H37" t="n">
-        <v>485</v>
+        <v>513</v>
       </c>
       <c r="I37" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="J37" t="n">
-        <v>482</v>
+        <v>427</v>
       </c>
       <c r="K37" t="n">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="L37" t="n">
-        <v>479.5</v>
+        <v>469.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>544</v>
+        <v>613</v>
       </c>
       <c r="C38" t="n">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="D38" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E38" t="n">
-        <v>614</v>
+        <v>532</v>
       </c>
       <c r="F38" t="n">
-        <v>681</v>
+        <v>561</v>
       </c>
       <c r="G38" t="n">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="H38" t="n">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="I38" t="n">
-        <v>607</v>
+        <v>521</v>
       </c>
       <c r="J38" t="n">
-        <v>598</v>
+        <v>516</v>
       </c>
       <c r="K38" t="n">
-        <v>632</v>
+        <v>682</v>
       </c>
       <c r="L38" t="n">
-        <v>590.1</v>
+        <v>564.8</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C39" t="n">
-        <v>470</v>
+        <v>414</v>
       </c>
       <c r="D39" t="n">
+        <v>398</v>
+      </c>
+      <c r="E39" t="n">
         <v>397</v>
       </c>
-      <c r="E39" t="n">
-        <v>412</v>
-      </c>
       <c r="F39" t="n">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="G39" t="n">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="H39" t="n">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="I39" t="n">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="J39" t="n">
-        <v>377</v>
+        <v>466</v>
       </c>
       <c r="K39" t="n">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="L39" t="n">
-        <v>418.9</v>
+        <v>417.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="C40" t="n">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="D40" t="n">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="E40" t="n">
-        <v>462</v>
+        <v>535</v>
       </c>
       <c r="F40" t="n">
-        <v>447</v>
+        <v>487</v>
       </c>
       <c r="G40" t="n">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="H40" t="n">
-        <v>462</v>
+        <v>518</v>
       </c>
       <c r="I40" t="n">
-        <v>525</v>
+        <v>484</v>
       </c>
       <c r="J40" t="n">
-        <v>504</v>
+        <v>465</v>
       </c>
       <c r="K40" t="n">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="L40" t="n">
-        <v>474.9</v>
+        <v>479.8</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="C41" t="n">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="D41" t="n">
-        <v>528</v>
+        <v>479</v>
       </c>
       <c r="E41" t="n">
-        <v>493</v>
+        <v>583</v>
       </c>
       <c r="F41" t="n">
-        <v>537</v>
+        <v>497</v>
       </c>
       <c r="G41" t="n">
-        <v>485</v>
+        <v>551</v>
       </c>
       <c r="H41" t="n">
-        <v>504</v>
+        <v>557</v>
       </c>
       <c r="I41" t="n">
-        <v>489</v>
+        <v>543</v>
       </c>
       <c r="J41" t="n">
-        <v>463</v>
+        <v>525</v>
       </c>
       <c r="K41" t="n">
-        <v>499</v>
+        <v>597</v>
       </c>
       <c r="L41" t="n">
-        <v>504.3</v>
+        <v>531.1</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C42" t="n">
+        <v>505</v>
+      </c>
+      <c r="D42" t="n">
+        <v>480</v>
+      </c>
+      <c r="E42" t="n">
+        <v>461</v>
+      </c>
+      <c r="F42" t="n">
+        <v>472</v>
+      </c>
+      <c r="G42" t="n">
+        <v>498</v>
+      </c>
+      <c r="H42" t="n">
         <v>532</v>
       </c>
-      <c r="D42" t="n">
-        <v>432</v>
-      </c>
-      <c r="E42" t="n">
-        <v>425</v>
-      </c>
-      <c r="F42" t="n">
-        <v>450</v>
-      </c>
-      <c r="G42" t="n">
-        <v>439</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
+        <v>524</v>
+      </c>
+      <c r="J42" t="n">
         <v>438</v>
       </c>
-      <c r="I42" t="n">
-        <v>425</v>
-      </c>
-      <c r="J42" t="n">
-        <v>469</v>
-      </c>
       <c r="K42" t="n">
-        <v>427</v>
+        <v>505</v>
       </c>
       <c r="L42" t="n">
-        <v>452.2</v>
+        <v>491.2</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="C43" t="n">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="D43" t="n">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="E43" t="n">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F43" t="n">
-        <v>513</v>
+        <v>466</v>
       </c>
       <c r="G43" t="n">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="H43" t="n">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="I43" t="n">
-        <v>530</v>
+        <v>450</v>
       </c>
       <c r="J43" t="n">
-        <v>474</v>
+        <v>516</v>
       </c>
       <c r="K43" t="n">
-        <v>482</v>
+        <v>515</v>
       </c>
       <c r="L43" t="n">
-        <v>488.3</v>
+        <v>486.3</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>483</v>
+        <v>418</v>
       </c>
       <c r="C44" t="n">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D44" t="n">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="E44" t="n">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="F44" t="n">
-        <v>447</v>
+        <v>527</v>
       </c>
       <c r="G44" t="n">
-        <v>427</v>
+        <v>515</v>
       </c>
       <c r="H44" t="n">
-        <v>457</v>
+        <v>397</v>
       </c>
       <c r="I44" t="n">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="J44" t="n">
-        <v>469</v>
+        <v>494</v>
       </c>
       <c r="K44" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="L44" t="n">
-        <v>456.6</v>
+        <v>460.8</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>521</v>
+        <v>473</v>
       </c>
       <c r="C45" t="n">
-        <v>494</v>
+        <v>459</v>
       </c>
       <c r="D45" t="n">
+        <v>501</v>
+      </c>
+      <c r="E45" t="n">
+        <v>467</v>
+      </c>
+      <c r="F45" t="n">
+        <v>437</v>
+      </c>
+      <c r="G45" t="n">
+        <v>471</v>
+      </c>
+      <c r="H45" t="n">
         <v>474</v>
       </c>
-      <c r="E45" t="n">
-        <v>413</v>
-      </c>
-      <c r="F45" t="n">
-        <v>474</v>
-      </c>
-      <c r="G45" t="n">
-        <v>483</v>
-      </c>
-      <c r="H45" t="n">
-        <v>486</v>
-      </c>
       <c r="I45" t="n">
-        <v>428</v>
+        <v>481</v>
       </c>
       <c r="J45" t="n">
-        <v>436</v>
+        <v>524</v>
       </c>
       <c r="K45" t="n">
-        <v>448</v>
+        <v>514</v>
       </c>
       <c r="L45" t="n">
-        <v>465.7</v>
+        <v>480.1</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>410</v>
+        <v>328</v>
       </c>
       <c r="C46" t="n">
-        <v>320</v>
+        <v>373</v>
       </c>
       <c r="D46" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E46" t="n">
-        <v>336</v>
+        <v>385</v>
       </c>
       <c r="F46" t="n">
-        <v>478</v>
+        <v>364</v>
       </c>
       <c r="G46" t="n">
-        <v>430</v>
+        <v>388</v>
       </c>
       <c r="H46" t="n">
-        <v>384</v>
+        <v>409</v>
       </c>
       <c r="I46" t="n">
+        <v>390</v>
+      </c>
+      <c r="J46" t="n">
+        <v>368</v>
+      </c>
+      <c r="K46" t="n">
         <v>397</v>
       </c>
-      <c r="J46" t="n">
-        <v>405</v>
-      </c>
-      <c r="K46" t="n">
-        <v>476</v>
-      </c>
       <c r="L46" t="n">
-        <v>402.8</v>
+        <v>379.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
+        <v>499</v>
+      </c>
+      <c r="C47" t="n">
+        <v>542</v>
+      </c>
+      <c r="D47" t="n">
+        <v>502</v>
+      </c>
+      <c r="E47" t="n">
+        <v>567</v>
+      </c>
+      <c r="F47" t="n">
+        <v>474</v>
+      </c>
+      <c r="G47" t="n">
+        <v>508</v>
+      </c>
+      <c r="H47" t="n">
         <v>523</v>
       </c>
-      <c r="C47" t="n">
-        <v>532</v>
-      </c>
-      <c r="D47" t="n">
-        <v>498</v>
-      </c>
-      <c r="E47" t="n">
-        <v>510</v>
-      </c>
-      <c r="F47" t="n">
-        <v>575</v>
-      </c>
-      <c r="G47" t="n">
-        <v>512</v>
-      </c>
-      <c r="H47" t="n">
-        <v>497</v>
-      </c>
       <c r="I47" t="n">
-        <v>519</v>
+        <v>602</v>
       </c>
       <c r="J47" t="n">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="K47" t="n">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="L47" t="n">
-        <v>523.7</v>
+        <v>534</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="C48" t="n">
-        <v>509</v>
+        <v>542</v>
       </c>
       <c r="D48" t="n">
-        <v>501</v>
+        <v>563</v>
       </c>
       <c r="E48" t="n">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="F48" t="n">
+        <v>500</v>
+      </c>
+      <c r="G48" t="n">
+        <v>521</v>
+      </c>
+      <c r="H48" t="n">
+        <v>522</v>
+      </c>
+      <c r="I48" t="n">
+        <v>533</v>
+      </c>
+      <c r="J48" t="n">
         <v>515</v>
       </c>
-      <c r="G48" t="n">
-        <v>497</v>
-      </c>
-      <c r="H48" t="n">
-        <v>483</v>
-      </c>
-      <c r="I48" t="n">
-        <v>560</v>
-      </c>
-      <c r="J48" t="n">
-        <v>557</v>
-      </c>
       <c r="K48" t="n">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="L48" t="n">
-        <v>517.8</v>
+        <v>524.9</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="C49" t="n">
-        <v>476</v>
+        <v>420</v>
       </c>
       <c r="D49" t="n">
-        <v>420</v>
+        <v>520</v>
       </c>
       <c r="E49" t="n">
-        <v>365</v>
+        <v>426</v>
       </c>
       <c r="F49" t="n">
-        <v>474</v>
+        <v>529</v>
       </c>
       <c r="G49" t="n">
-        <v>489</v>
+        <v>525</v>
       </c>
       <c r="H49" t="n">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="I49" t="n">
-        <v>529</v>
+        <v>461</v>
       </c>
       <c r="J49" t="n">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="K49" t="n">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="L49" t="n">
-        <v>464.7</v>
+        <v>476.8</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="C50" t="n">
-        <v>454</v>
+        <v>426</v>
       </c>
       <c r="D50" t="n">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="E50" t="n">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="F50" t="n">
-        <v>484</v>
+        <v>406</v>
       </c>
       <c r="G50" t="n">
-        <v>505</v>
+        <v>434</v>
       </c>
       <c r="H50" t="n">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="I50" t="n">
-        <v>477</v>
+        <v>400</v>
       </c>
       <c r="J50" t="n">
-        <v>494</v>
+        <v>430</v>
       </c>
       <c r="K50" t="n">
-        <v>484</v>
+        <v>432</v>
       </c>
       <c r="L50" t="n">
-        <v>477.5</v>
+        <v>437.4</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="C51" t="n">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="D51" t="n">
-        <v>426</v>
+        <v>497</v>
       </c>
       <c r="E51" t="n">
-        <v>448</v>
+        <v>477</v>
       </c>
       <c r="F51" t="n">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="G51" t="n">
-        <v>432</v>
+        <v>465</v>
       </c>
       <c r="H51" t="n">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="I51" t="n">
-        <v>433</v>
+        <v>487</v>
       </c>
       <c r="J51" t="n">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="K51" t="n">
-        <v>401</v>
+        <v>486</v>
       </c>
       <c r="L51" t="n">
-        <v>439.3</v>
+        <v>467.2</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>474.64</v>
+        <v>475.54</v>
       </c>
       <c r="C52" t="n">
-        <v>485</v>
+        <v>482.1</v>
       </c>
       <c r="D52" t="n">
-        <v>471.3</v>
+        <v>478.84</v>
       </c>
       <c r="E52" t="n">
-        <v>476.14</v>
+        <v>488.06</v>
       </c>
       <c r="F52" t="n">
-        <v>484.3</v>
+        <v>477.56</v>
       </c>
       <c r="G52" t="n">
-        <v>471.32</v>
+        <v>479.42</v>
       </c>
       <c r="H52" t="n">
-        <v>479.74</v>
+        <v>484.44</v>
       </c>
       <c r="I52" t="n">
-        <v>479.7</v>
+        <v>477.66</v>
       </c>
       <c r="J52" t="n">
-        <v>475.36</v>
+        <v>474.78</v>
       </c>
       <c r="K52" t="n">
-        <v>482.86</v>
+        <v>486.1</v>
       </c>
       <c r="L52" t="n">
-        <v>478.036</v>
+        <v>480.45</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.518785715103149</v>
+        <v>2.651631116867065</v>
       </c>
       <c r="C2" t="n">
-        <v>3.051668167114258</v>
+        <v>3.713479042053223</v>
       </c>
       <c r="D2" t="n">
-        <v>2.615121603012085</v>
+        <v>2.426350593566895</v>
       </c>
       <c r="E2" t="n">
-        <v>4.216107368469238</v>
+        <v>2.345524787902832</v>
       </c>
       <c r="F2" t="n">
-        <v>2.661339998245239</v>
+        <v>3.312138795852661</v>
       </c>
       <c r="G2" t="n">
-        <v>2.408356428146362</v>
+        <v>2.078209161758423</v>
       </c>
       <c r="H2" t="n">
-        <v>2.285431146621704</v>
+        <v>2.136059045791626</v>
       </c>
       <c r="I2" t="n">
-        <v>2.523486852645874</v>
+        <v>2.238806962966919</v>
       </c>
       <c r="J2" t="n">
-        <v>2.905663251876831</v>
+        <v>2.127077341079712</v>
       </c>
       <c r="K2" t="n">
-        <v>3.276240110397339</v>
+        <v>2.171954870223999</v>
       </c>
       <c r="L2" t="n">
-        <v>2.846220064163208</v>
+        <v>2.520123171806335</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.647231340408325</v>
+        <v>2.22931694984436</v>
       </c>
       <c r="C3" t="n">
-        <v>2.428138971328735</v>
+        <v>2.256247043609619</v>
       </c>
       <c r="D3" t="n">
-        <v>2.635607481002808</v>
+        <v>2.211392164230347</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9513258934021</v>
+        <v>2.504122018814087</v>
       </c>
       <c r="F3" t="n">
-        <v>2.41429615020752</v>
+        <v>2.435299396514893</v>
       </c>
       <c r="G3" t="n">
-        <v>2.398709535598755</v>
+        <v>2.394897222518921</v>
       </c>
       <c r="H3" t="n">
-        <v>2.284925937652588</v>
+        <v>2.355500936508179</v>
       </c>
       <c r="I3" t="n">
-        <v>2.731849908828735</v>
+        <v>2.398894548416138</v>
       </c>
       <c r="J3" t="n">
-        <v>2.968387126922607</v>
+        <v>2.321573257446289</v>
       </c>
       <c r="K3" t="n">
-        <v>2.555915594100952</v>
+        <v>2.210352420806885</v>
       </c>
       <c r="L3" t="n">
-        <v>2.601638793945312</v>
+        <v>2.331759595870972</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>3.657440185546875</v>
+        <v>2.405879974365234</v>
       </c>
       <c r="C4" t="n">
-        <v>2.82404088973999</v>
+        <v>2.610339879989624</v>
       </c>
       <c r="D4" t="n">
-        <v>2.492300987243652</v>
+        <v>2.269334077835083</v>
       </c>
       <c r="E4" t="n">
-        <v>2.627210378646851</v>
+        <v>2.462097406387329</v>
       </c>
       <c r="F4" t="n">
-        <v>2.718798398971558</v>
+        <v>2.527923345565796</v>
       </c>
       <c r="G4" t="n">
-        <v>2.933516025543213</v>
+        <v>2.552916765213013</v>
       </c>
       <c r="H4" t="n">
-        <v>2.719066381454468</v>
+        <v>2.304500341415405</v>
       </c>
       <c r="I4" t="n">
-        <v>2.443994522094727</v>
+        <v>2.845698118209839</v>
       </c>
       <c r="J4" t="n">
-        <v>2.518493413925171</v>
+        <v>2.982968330383301</v>
       </c>
       <c r="K4" t="n">
-        <v>2.521199226379395</v>
+        <v>2.767975091934204</v>
       </c>
       <c r="L4" t="n">
-        <v>2.74560604095459</v>
+        <v>2.572963333129883</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>2.330038070678711</v>
+        <v>2.164474725723267</v>
       </c>
       <c r="C5" t="n">
-        <v>2.260169506072998</v>
+        <v>2.235296964645386</v>
       </c>
       <c r="D5" t="n">
-        <v>2.221444845199585</v>
+        <v>2.211374521255493</v>
       </c>
       <c r="E5" t="n">
-        <v>2.062414169311523</v>
+        <v>2.19340991973877</v>
       </c>
       <c r="F5" t="n">
-        <v>2.334825038909912</v>
+        <v>2.232295513153076</v>
       </c>
       <c r="G5" t="n">
-        <v>2.338768005371094</v>
+        <v>2.326075553894043</v>
       </c>
       <c r="H5" t="n">
-        <v>2.294439077377319</v>
+        <v>2.171949148178101</v>
       </c>
       <c r="I5" t="n">
-        <v>2.160462379455566</v>
+        <v>2.295678615570068</v>
       </c>
       <c r="J5" t="n">
-        <v>2.208476305007935</v>
+        <v>2.5376296043396</v>
       </c>
       <c r="K5" t="n">
-        <v>2.117707490921021</v>
+        <v>2.462215662002563</v>
       </c>
       <c r="L5" t="n">
-        <v>2.232874488830566</v>
+        <v>2.283040022850037</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>2.16595458984375</v>
+        <v>2.208250045776367</v>
       </c>
       <c r="C6" t="n">
-        <v>2.373256683349609</v>
+        <v>2.107035875320435</v>
       </c>
       <c r="D6" t="n">
-        <v>2.354365110397339</v>
+        <v>2.075100183486938</v>
       </c>
       <c r="E6" t="n">
-        <v>2.403001546859741</v>
+        <v>1.941441774368286</v>
       </c>
       <c r="F6" t="n">
-        <v>2.198363780975342</v>
+        <v>1.958286285400391</v>
       </c>
       <c r="G6" t="n">
-        <v>2.008662939071655</v>
+        <v>1.999917507171631</v>
       </c>
       <c r="H6" t="n">
-        <v>2.094183921813965</v>
+        <v>2.448774576187134</v>
       </c>
       <c r="I6" t="n">
-        <v>2.084811449050903</v>
+        <v>2.26575493812561</v>
       </c>
       <c r="J6" t="n">
-        <v>2.093677043914795</v>
+        <v>2.246292352676392</v>
       </c>
       <c r="K6" t="n">
-        <v>1.916215181350708</v>
+        <v>2.384950160980225</v>
       </c>
       <c r="L6" t="n">
-        <v>2.169249224662781</v>
+        <v>2.163580369949341</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.593456983566284</v>
+        <v>2.527069091796875</v>
       </c>
       <c r="C7" t="n">
-        <v>2.941132783889771</v>
+        <v>2.743549108505249</v>
       </c>
       <c r="D7" t="n">
-        <v>2.380005121231079</v>
+        <v>3.062276840209961</v>
       </c>
       <c r="E7" t="n">
-        <v>2.431841850280762</v>
+        <v>3.113143682479858</v>
       </c>
       <c r="F7" t="n">
-        <v>2.763509273529053</v>
+        <v>2.590924024581909</v>
       </c>
       <c r="G7" t="n">
-        <v>2.648690700531006</v>
+        <v>2.257775545120239</v>
       </c>
       <c r="H7" t="n">
-        <v>2.462903261184692</v>
+        <v>2.216357707977295</v>
       </c>
       <c r="I7" t="n">
-        <v>2.574195146560669</v>
+        <v>2.36600661277771</v>
       </c>
       <c r="J7" t="n">
-        <v>2.514870643615723</v>
+        <v>2.174958467483521</v>
       </c>
       <c r="K7" t="n">
-        <v>2.665378332138062</v>
+        <v>2.580481052398682</v>
       </c>
       <c r="L7" t="n">
-        <v>2.59759840965271</v>
+        <v>2.56325421333313</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.492516756057739</v>
+        <v>2.574493169784546</v>
       </c>
       <c r="C8" t="n">
-        <v>2.727102279663086</v>
+        <v>2.610361099243164</v>
       </c>
       <c r="D8" t="n">
-        <v>2.486640453338623</v>
+        <v>2.253259420394897</v>
       </c>
       <c r="E8" t="n">
-        <v>2.490798950195312</v>
+        <v>2.369995832443237</v>
       </c>
       <c r="F8" t="n">
-        <v>2.689989328384399</v>
+        <v>2.334553241729736</v>
       </c>
       <c r="G8" t="n">
-        <v>2.671957731246948</v>
+        <v>2.589410543441772</v>
       </c>
       <c r="H8" t="n">
-        <v>2.570642709732056</v>
+        <v>2.342048168182373</v>
       </c>
       <c r="I8" t="n">
-        <v>2.365232229232788</v>
+        <v>2.187918186187744</v>
       </c>
       <c r="J8" t="n">
-        <v>2.439267635345459</v>
+        <v>2.220868110656738</v>
       </c>
       <c r="K8" t="n">
-        <v>2.643036842346191</v>
+        <v>2.273208141326904</v>
       </c>
       <c r="L8" t="n">
-        <v>2.55771849155426</v>
+        <v>2.375611591339111</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.427645444869995</v>
+        <v>2.099170207977295</v>
       </c>
       <c r="C9" t="n">
-        <v>2.455801486968994</v>
+        <v>2.535049200057983</v>
       </c>
       <c r="D9" t="n">
-        <v>2.493570804595947</v>
+        <v>2.200924396514893</v>
       </c>
       <c r="E9" t="n">
-        <v>2.425484895706177</v>
+        <v>2.203391790390015</v>
       </c>
       <c r="F9" t="n">
-        <v>2.243837356567383</v>
+        <v>2.20039701461792</v>
       </c>
       <c r="G9" t="n">
-        <v>2.234189033508301</v>
+        <v>2.337069272994995</v>
       </c>
       <c r="H9" t="n">
-        <v>2.36250376701355</v>
+        <v>2.142055511474609</v>
       </c>
       <c r="I9" t="n">
-        <v>2.341644287109375</v>
+        <v>2.334578275680542</v>
       </c>
       <c r="J9" t="n">
-        <v>2.216802358627319</v>
+        <v>2.208392381668091</v>
       </c>
       <c r="K9" t="n">
-        <v>2.493381977081299</v>
+        <v>2.19940447807312</v>
       </c>
       <c r="L9" t="n">
-        <v>2.369486141204834</v>
+        <v>2.246043252944946</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.198734283447266</v>
+        <v>2.277753353118896</v>
       </c>
       <c r="C10" t="n">
-        <v>2.167588472366333</v>
+        <v>2.386945724487305</v>
       </c>
       <c r="D10" t="n">
-        <v>2.258934259414673</v>
+        <v>2.267816066741943</v>
       </c>
       <c r="E10" t="n">
-        <v>2.311743259429932</v>
+        <v>2.40691614151001</v>
       </c>
       <c r="F10" t="n">
-        <v>2.104882955551147</v>
+        <v>2.197411060333252</v>
       </c>
       <c r="G10" t="n">
-        <v>2.127909660339355</v>
+        <v>2.377464532852173</v>
       </c>
       <c r="H10" t="n">
-        <v>2.422099113464355</v>
+        <v>2.185468435287476</v>
       </c>
       <c r="I10" t="n">
-        <v>2.163040161132812</v>
+        <v>2.157527446746826</v>
       </c>
       <c r="J10" t="n">
-        <v>2.279372692108154</v>
+        <v>2.339544773101807</v>
       </c>
       <c r="K10" t="n">
-        <v>2.278149366378784</v>
+        <v>2.377996921539307</v>
       </c>
       <c r="L10" t="n">
-        <v>2.231245422363281</v>
+        <v>2.297484445571899</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>2.014990091323853</v>
+        <v>2.291610717773438</v>
       </c>
       <c r="C11" t="n">
-        <v>1.837619781494141</v>
+        <v>1.878129720687866</v>
       </c>
       <c r="D11" t="n">
-        <v>2.047646284103394</v>
+        <v>1.844696998596191</v>
       </c>
       <c r="E11" t="n">
-        <v>2.127836465835571</v>
+        <v>2.066777467727661</v>
       </c>
       <c r="F11" t="n">
-        <v>1.966526985168457</v>
+        <v>2.004901885986328</v>
       </c>
       <c r="G11" t="n">
-        <v>2.035453319549561</v>
+        <v>1.850289344787598</v>
       </c>
       <c r="H11" t="n">
-        <v>1.882844924926758</v>
+        <v>2.040824413299561</v>
       </c>
       <c r="I11" t="n">
-        <v>2.022356986999512</v>
+        <v>1.940064191818237</v>
       </c>
       <c r="J11" t="n">
-        <v>2.058540105819702</v>
+        <v>2.113130331039429</v>
       </c>
       <c r="K11" t="n">
-        <v>1.911655426025391</v>
+        <v>2.063752174377441</v>
       </c>
       <c r="L11" t="n">
-        <v>1.990547037124634</v>
+        <v>2.009417724609375</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.060028553009033</v>
+        <v>2.259297132492065</v>
       </c>
       <c r="C12" t="n">
-        <v>2.209533452987671</v>
+        <v>2.249293327331543</v>
       </c>
       <c r="D12" t="n">
-        <v>2.207765579223633</v>
+        <v>2.069728136062622</v>
       </c>
       <c r="E12" t="n">
-        <v>2.377715587615967</v>
+        <v>2.399917602539062</v>
       </c>
       <c r="F12" t="n">
-        <v>2.07909107208252</v>
+        <v>2.514660358428955</v>
       </c>
       <c r="G12" t="n">
-        <v>2.73294472694397</v>
+        <v>2.312570571899414</v>
       </c>
       <c r="H12" t="n">
-        <v>2.469961881637573</v>
+        <v>2.145898342132568</v>
       </c>
       <c r="I12" t="n">
-        <v>2.312042236328125</v>
+        <v>2.21027684211731</v>
       </c>
       <c r="J12" t="n">
-        <v>2.185241937637329</v>
+        <v>2.225253343582153</v>
       </c>
       <c r="K12" t="n">
-        <v>2.138395071029663</v>
+        <v>2.253148794174194</v>
       </c>
       <c r="L12" t="n">
-        <v>2.277272009849548</v>
+        <v>2.264004445075989</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.368075609207153</v>
+        <v>2.275071382522583</v>
       </c>
       <c r="C13" t="n">
-        <v>2.356703996658325</v>
+        <v>2.151396512985229</v>
       </c>
       <c r="D13" t="n">
-        <v>2.159152269363403</v>
+        <v>2.203262567520142</v>
       </c>
       <c r="E13" t="n">
-        <v>2.528008222579956</v>
+        <v>2.251128673553467</v>
       </c>
       <c r="F13" t="n">
-        <v>2.271748781204224</v>
+        <v>2.306503295898438</v>
       </c>
       <c r="G13" t="n">
-        <v>2.376585721969604</v>
+        <v>2.210241079330444</v>
       </c>
       <c r="H13" t="n">
-        <v>2.61954927444458</v>
+        <v>2.313472747802734</v>
       </c>
       <c r="I13" t="n">
-        <v>2.178174257278442</v>
+        <v>2.414729833602905</v>
       </c>
       <c r="J13" t="n">
-        <v>2.195983171463013</v>
+        <v>2.262614965438843</v>
       </c>
       <c r="K13" t="n">
-        <v>2.358962774276733</v>
+        <v>2.606221437454224</v>
       </c>
       <c r="L13" t="n">
-        <v>2.341294407844543</v>
+        <v>2.299464249610901</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.497351169586182</v>
+        <v>2.278563737869263</v>
       </c>
       <c r="C14" t="n">
-        <v>2.254577398300171</v>
+        <v>2.334412813186646</v>
       </c>
       <c r="D14" t="n">
-        <v>2.229988098144531</v>
+        <v>2.323951244354248</v>
       </c>
       <c r="E14" t="n">
-        <v>2.228809595108032</v>
+        <v>2.368332862854004</v>
       </c>
       <c r="F14" t="n">
-        <v>2.069144010543823</v>
+        <v>2.214229822158813</v>
       </c>
       <c r="G14" t="n">
-        <v>2.611741304397583</v>
+        <v>2.356862306594849</v>
       </c>
       <c r="H14" t="n">
-        <v>2.30187201499939</v>
+        <v>2.322454214096069</v>
       </c>
       <c r="I14" t="n">
-        <v>2.224338293075562</v>
+        <v>2.278573036193848</v>
       </c>
       <c r="J14" t="n">
-        <v>2.225438833236694</v>
+        <v>2.451620817184448</v>
       </c>
       <c r="K14" t="n">
-        <v>2.432707548141479</v>
+        <v>2.574308633804321</v>
       </c>
       <c r="L14" t="n">
-        <v>2.307596826553345</v>
+        <v>2.350330948829651</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2.392907619476318</v>
+        <v>2.169346570968628</v>
       </c>
       <c r="C15" t="n">
-        <v>2.233919143676758</v>
+        <v>2.166865825653076</v>
       </c>
       <c r="D15" t="n">
-        <v>2.206415414810181</v>
+        <v>2.251659870147705</v>
       </c>
       <c r="E15" t="n">
-        <v>2.417206048965454</v>
+        <v>2.274075031280518</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2181556224823</v>
+        <v>2.18731164932251</v>
       </c>
       <c r="G15" t="n">
-        <v>2.049375534057617</v>
+        <v>2.163362741470337</v>
       </c>
       <c r="H15" t="n">
-        <v>2.195311307907104</v>
+        <v>2.295534372329712</v>
       </c>
       <c r="I15" t="n">
-        <v>2.181085824966431</v>
+        <v>2.204270362854004</v>
       </c>
       <c r="J15" t="n">
-        <v>2.369036912918091</v>
+        <v>2.172837018966675</v>
       </c>
       <c r="K15" t="n">
-        <v>2.281201601028442</v>
+        <v>2.143419981002808</v>
       </c>
       <c r="L15" t="n">
-        <v>2.25446150302887</v>
+        <v>2.202868342399597</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.360722303390503</v>
+        <v>2.16385817527771</v>
       </c>
       <c r="C16" t="n">
-        <v>2.233148574829102</v>
+        <v>2.458097457885742</v>
       </c>
       <c r="D16" t="n">
-        <v>2.203218936920166</v>
+        <v>2.44762396812439</v>
       </c>
       <c r="E16" t="n">
-        <v>2.28692364692688</v>
+        <v>2.452118158340454</v>
       </c>
       <c r="F16" t="n">
-        <v>2.131868839263916</v>
+        <v>2.303501129150391</v>
       </c>
       <c r="G16" t="n">
-        <v>2.289784669876099</v>
+        <v>2.497996807098389</v>
       </c>
       <c r="H16" t="n">
-        <v>2.20766019821167</v>
+        <v>2.398779630661011</v>
       </c>
       <c r="I16" t="n">
-        <v>2.261330366134644</v>
+        <v>2.391769647598267</v>
       </c>
       <c r="J16" t="n">
-        <v>2.39049506187439</v>
+        <v>2.407718658447266</v>
       </c>
       <c r="K16" t="n">
-        <v>2.129012107849121</v>
+        <v>2.221208333969116</v>
       </c>
       <c r="L16" t="n">
-        <v>2.249416470527649</v>
+        <v>2.374267196655274</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1.951903104782104</v>
+        <v>2.094049453735352</v>
       </c>
       <c r="C17" t="n">
-        <v>2.175958156585693</v>
+        <v>2.254136323928833</v>
       </c>
       <c r="D17" t="n">
-        <v>2.248831033706665</v>
+        <v>2.152398824691772</v>
       </c>
       <c r="E17" t="n">
-        <v>2.17115592956543</v>
+        <v>2.156025409698486</v>
       </c>
       <c r="F17" t="n">
-        <v>2.303900718688965</v>
+        <v>2.105125904083252</v>
       </c>
       <c r="G17" t="n">
-        <v>2.151848077774048</v>
+        <v>2.550532341003418</v>
       </c>
       <c r="H17" t="n">
-        <v>2.125126600265503</v>
+        <v>2.254251718521118</v>
       </c>
       <c r="I17" t="n">
-        <v>2.282006025314331</v>
+        <v>2.463251352310181</v>
       </c>
       <c r="J17" t="n">
-        <v>1.988137722015381</v>
+        <v>2.129065990447998</v>
       </c>
       <c r="K17" t="n">
-        <v>2.345203399658203</v>
+        <v>2.239378690719604</v>
       </c>
       <c r="L17" t="n">
-        <v>2.174407076835633</v>
+        <v>2.239821600914001</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>2.881525754928589</v>
+        <v>2.295151710510254</v>
       </c>
       <c r="C18" t="n">
-        <v>2.402466535568237</v>
+        <v>2.505110263824463</v>
       </c>
       <c r="D18" t="n">
-        <v>2.443566560745239</v>
+        <v>2.409854173660278</v>
       </c>
       <c r="E18" t="n">
-        <v>2.354500770568848</v>
+        <v>2.367965459823608</v>
       </c>
       <c r="F18" t="n">
-        <v>2.332955360412598</v>
+        <v>2.473201751708984</v>
       </c>
       <c r="G18" t="n">
-        <v>2.491391181945801</v>
+        <v>2.407863855361938</v>
       </c>
       <c r="H18" t="n">
-        <v>2.598001718521118</v>
+        <v>2.350506067276001</v>
       </c>
       <c r="I18" t="n">
-        <v>2.398101806640625</v>
+        <v>2.410860061645508</v>
       </c>
       <c r="J18" t="n">
-        <v>2.521090030670166</v>
+        <v>2.497141122817993</v>
       </c>
       <c r="K18" t="n">
-        <v>2.42997932434082</v>
+        <v>2.458247900009155</v>
       </c>
       <c r="L18" t="n">
-        <v>2.485357904434204</v>
+        <v>2.417590236663818</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.285372495651245</v>
+        <v>2.364456415176392</v>
       </c>
       <c r="C19" t="n">
-        <v>2.209100484848022</v>
+        <v>2.458730459213257</v>
       </c>
       <c r="D19" t="n">
-        <v>2.333390951156616</v>
+        <v>2.302632331848145</v>
       </c>
       <c r="E19" t="n">
-        <v>2.363886117935181</v>
+        <v>2.455254077911377</v>
       </c>
       <c r="F19" t="n">
-        <v>2.334386110305786</v>
+        <v>2.412840127944946</v>
       </c>
       <c r="G19" t="n">
-        <v>2.740038871765137</v>
+        <v>2.35149097442627</v>
       </c>
       <c r="H19" t="n">
-        <v>2.446236133575439</v>
+        <v>2.378942012786865</v>
       </c>
       <c r="I19" t="n">
-        <v>2.429028987884521</v>
+        <v>2.295666456222534</v>
       </c>
       <c r="J19" t="n">
-        <v>2.434893369674683</v>
+        <v>2.378440618515015</v>
       </c>
       <c r="K19" t="n">
-        <v>2.543171405792236</v>
+        <v>2.379421234130859</v>
       </c>
       <c r="L19" t="n">
-        <v>2.411950492858887</v>
+        <v>2.377787470817566</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.264900207519531</v>
+        <v>2.489191770553589</v>
       </c>
       <c r="C20" t="n">
-        <v>2.275371789932251</v>
+        <v>2.483173847198486</v>
       </c>
       <c r="D20" t="n">
-        <v>2.511718273162842</v>
+        <v>2.308615207672119</v>
       </c>
       <c r="E20" t="n">
-        <v>2.219542503356934</v>
+        <v>2.337547063827515</v>
       </c>
       <c r="F20" t="n">
-        <v>2.32935643196106</v>
+        <v>2.196390151977539</v>
       </c>
       <c r="G20" t="n">
-        <v>2.421076774597168</v>
+        <v>2.200409650802612</v>
       </c>
       <c r="H20" t="n">
-        <v>2.167277812957764</v>
+        <v>2.42481541633606</v>
       </c>
       <c r="I20" t="n">
-        <v>2.048961400985718</v>
+        <v>2.151539325714111</v>
       </c>
       <c r="J20" t="n">
-        <v>2.162894725799561</v>
+        <v>2.398885726928711</v>
       </c>
       <c r="K20" t="n">
-        <v>2.157275438308716</v>
+        <v>2.279183149337769</v>
       </c>
       <c r="L20" t="n">
-        <v>2.255837535858154</v>
+        <v>2.326975131034851</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.187392473220825</v>
+        <v>2.454248189926147</v>
       </c>
       <c r="C21" t="n">
-        <v>2.448850870132446</v>
+        <v>2.230317831039429</v>
       </c>
       <c r="D21" t="n">
-        <v>2.453166246414185</v>
+        <v>2.253759384155273</v>
       </c>
       <c r="E21" t="n">
-        <v>2.379637002944946</v>
+        <v>2.197377920150757</v>
       </c>
       <c r="F21" t="n">
-        <v>2.331957101821899</v>
+        <v>2.592400312423706</v>
       </c>
       <c r="G21" t="n">
-        <v>2.378220081329346</v>
+        <v>2.171947240829468</v>
       </c>
       <c r="H21" t="n">
-        <v>2.437948226928711</v>
+        <v>2.351006984710693</v>
       </c>
       <c r="I21" t="n">
-        <v>2.486387252807617</v>
+        <v>2.303627967834473</v>
       </c>
       <c r="J21" t="n">
-        <v>2.186733961105347</v>
+        <v>2.224324226379395</v>
       </c>
       <c r="K21" t="n">
-        <v>2.293241262435913</v>
+        <v>2.178449392318726</v>
       </c>
       <c r="L21" t="n">
-        <v>2.358353447914124</v>
+        <v>2.295745944976807</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.140374660491943</v>
+        <v>2.268211603164673</v>
       </c>
       <c r="C22" t="n">
-        <v>2.313931226730347</v>
+        <v>2.197366714477539</v>
       </c>
       <c r="D22" t="n">
-        <v>2.04208517074585</v>
+        <v>2.099154710769653</v>
       </c>
       <c r="E22" t="n">
-        <v>2.301247358322144</v>
+        <v>2.253764390945435</v>
       </c>
       <c r="F22" t="n">
-        <v>2.070802927017212</v>
+        <v>2.214353799819946</v>
       </c>
       <c r="G22" t="n">
-        <v>2.279967546463013</v>
+        <v>2.207370281219482</v>
       </c>
       <c r="H22" t="n">
-        <v>2.11380672454834</v>
+        <v>2.531054258346558</v>
       </c>
       <c r="I22" t="n">
-        <v>2.153233289718628</v>
+        <v>2.158519506454468</v>
       </c>
       <c r="J22" t="n">
-        <v>2.191608428955078</v>
+        <v>2.26821494102478</v>
       </c>
       <c r="K22" t="n">
-        <v>2.064438104629517</v>
+        <v>2.364977359771729</v>
       </c>
       <c r="L22" t="n">
-        <v>2.167149543762207</v>
+        <v>2.256298756599426</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>2.097695350646973</v>
+        <v>1.918607711791992</v>
       </c>
       <c r="C23" t="n">
-        <v>1.911341667175293</v>
+        <v>2.075205087661743</v>
       </c>
       <c r="D23" t="n">
-        <v>1.965445995330811</v>
+        <v>2.159991979598999</v>
       </c>
       <c r="E23" t="n">
-        <v>1.927299737930298</v>
+        <v>2.214871883392334</v>
       </c>
       <c r="F23" t="n">
-        <v>2.008274078369141</v>
+        <v>2.042789220809937</v>
       </c>
       <c r="G23" t="n">
-        <v>1.855539083480835</v>
+        <v>2.027827501296997</v>
       </c>
       <c r="H23" t="n">
-        <v>2.008226871490479</v>
+        <v>1.9739670753479</v>
       </c>
       <c r="I23" t="n">
-        <v>1.928768634796143</v>
+        <v>2.227325439453125</v>
       </c>
       <c r="J23" t="n">
-        <v>2.055017709732056</v>
+        <v>2.000903129577637</v>
       </c>
       <c r="K23" t="n">
-        <v>2.010097980499268</v>
+        <v>2.134063720703125</v>
       </c>
       <c r="L23" t="n">
-        <v>1.976770710945129</v>
+        <v>2.077555274963379</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>2.078308343887329</v>
+        <v>2.103132486343384</v>
       </c>
       <c r="C24" t="n">
-        <v>2.222287893295288</v>
+        <v>2.283719778060913</v>
       </c>
       <c r="D24" t="n">
-        <v>2.156919240951538</v>
+        <v>2.150526285171509</v>
       </c>
       <c r="E24" t="n">
-        <v>2.073009252548218</v>
+        <v>2.016851663589478</v>
       </c>
       <c r="F24" t="n">
-        <v>1.962282180786133</v>
+        <v>1.99889874458313</v>
       </c>
       <c r="G24" t="n">
-        <v>2.165767192840576</v>
+        <v>2.044783592224121</v>
       </c>
       <c r="H24" t="n">
-        <v>2.164836645126343</v>
+        <v>1.960009813308716</v>
       </c>
       <c r="I24" t="n">
-        <v>2.087508916854858</v>
+        <v>2.109131574630737</v>
       </c>
       <c r="J24" t="n">
-        <v>2.01750922203064</v>
+        <v>2.031818389892578</v>
       </c>
       <c r="K24" t="n">
-        <v>2.265412330627441</v>
+        <v>2.177457094192505</v>
       </c>
       <c r="L24" t="n">
-        <v>2.119384121894837</v>
+        <v>2.087632942199707</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.572502136230469</v>
+        <v>2.277693271636963</v>
       </c>
       <c r="C25" t="n">
-        <v>2.208948373794556</v>
+        <v>2.303622245788574</v>
       </c>
       <c r="D25" t="n">
-        <v>2.052402019500732</v>
+        <v>2.344522714614868</v>
       </c>
       <c r="E25" t="n">
-        <v>2.275273561477661</v>
+        <v>2.260232925415039</v>
       </c>
       <c r="F25" t="n">
-        <v>2.193240404129028</v>
+        <v>2.5096275806427</v>
       </c>
       <c r="G25" t="n">
-        <v>2.250656127929688</v>
+        <v>2.374451875686646</v>
       </c>
       <c r="H25" t="n">
-        <v>2.291579723358154</v>
+        <v>2.26572585105896</v>
       </c>
       <c r="I25" t="n">
-        <v>2.117990493774414</v>
+        <v>2.256248712539673</v>
       </c>
       <c r="J25" t="n">
-        <v>2.051986932754517</v>
+        <v>2.194407939910889</v>
       </c>
       <c r="K25" t="n">
-        <v>2.378409147262573</v>
+        <v>2.295636653900146</v>
       </c>
       <c r="L25" t="n">
-        <v>2.239298892021179</v>
+        <v>2.308216977119446</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.178070783615112</v>
+        <v>2.534540891647339</v>
       </c>
       <c r="C26" t="n">
-        <v>2.340244054794312</v>
+        <v>2.575924396514893</v>
       </c>
       <c r="D26" t="n">
-        <v>2.261166095733643</v>
+        <v>2.445281028747559</v>
       </c>
       <c r="E26" t="n">
-        <v>2.23963475227356</v>
+        <v>2.269208192825317</v>
       </c>
       <c r="F26" t="n">
-        <v>2.438210248947144</v>
+        <v>2.370955228805542</v>
       </c>
       <c r="G26" t="n">
-        <v>2.395162582397461</v>
+        <v>2.443768978118896</v>
       </c>
       <c r="H26" t="n">
-        <v>2.56738018989563</v>
+        <v>2.383932828903198</v>
       </c>
       <c r="I26" t="n">
-        <v>2.252784729003906</v>
+        <v>2.397882699966431</v>
       </c>
       <c r="J26" t="n">
-        <v>2.426821708679199</v>
+        <v>2.380931377410889</v>
       </c>
       <c r="K26" t="n">
-        <v>2.408629179000854</v>
+        <v>2.405864000320435</v>
       </c>
       <c r="L26" t="n">
-        <v>2.350810432434082</v>
+        <v>2.42082896232605</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>2.162241458892822</v>
+        <v>2.332558155059814</v>
       </c>
       <c r="C27" t="n">
-        <v>2.196434497833252</v>
+        <v>2.137552738189697</v>
       </c>
       <c r="D27" t="n">
-        <v>2.229543209075928</v>
+        <v>2.293147563934326</v>
       </c>
       <c r="E27" t="n">
-        <v>2.28376841545105</v>
+        <v>2.067223072052002</v>
       </c>
       <c r="F27" t="n">
-        <v>2.170157909393311</v>
+        <v>2.147553205490112</v>
       </c>
       <c r="G27" t="n">
-        <v>2.229762554168701</v>
+        <v>2.234309673309326</v>
       </c>
       <c r="H27" t="n">
-        <v>2.258485555648804</v>
+        <v>2.117113351821899</v>
       </c>
       <c r="I27" t="n">
-        <v>2.241619825363159</v>
+        <v>2.164505958557129</v>
       </c>
       <c r="J27" t="n">
-        <v>2.286272287368774</v>
+        <v>2.128075361251831</v>
       </c>
       <c r="K27" t="n">
-        <v>2.219148874282837</v>
+        <v>2.424828290939331</v>
       </c>
       <c r="L27" t="n">
-        <v>2.227743458747864</v>
+        <v>2.204686737060547</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.0842604637146</v>
+        <v>2.284682035446167</v>
       </c>
       <c r="C28" t="n">
-        <v>2.061794996261597</v>
+        <v>2.198405504226685</v>
       </c>
       <c r="D28" t="n">
-        <v>2.054548501968384</v>
+        <v>2.081190586090088</v>
       </c>
       <c r="E28" t="n">
-        <v>2.131154298782349</v>
+        <v>2.197416543960571</v>
       </c>
       <c r="F28" t="n">
-        <v>1.966502904891968</v>
+        <v>2.089662790298462</v>
       </c>
       <c r="G28" t="n">
-        <v>2.105685949325562</v>
+        <v>2.17445969581604</v>
       </c>
       <c r="H28" t="n">
-        <v>2.039618015289307</v>
+        <v>2.16848349571228</v>
       </c>
       <c r="I28" t="n">
-        <v>2.233747720718384</v>
+        <v>2.144025564193726</v>
       </c>
       <c r="J28" t="n">
-        <v>1.948415756225586</v>
+        <v>2.167479038238525</v>
       </c>
       <c r="K28" t="n">
-        <v>2.100440979003906</v>
+        <v>2.18143892288208</v>
       </c>
       <c r="L28" t="n">
-        <v>2.072616958618164</v>
+        <v>2.168724417686462</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>2.036488771438599</v>
+        <v>2.135057926177979</v>
       </c>
       <c r="C29" t="n">
-        <v>2.150121450424194</v>
+        <v>2.145023345947266</v>
       </c>
       <c r="D29" t="n">
-        <v>2.297465085983276</v>
+        <v>2.180447101593018</v>
       </c>
       <c r="E29" t="n">
-        <v>2.223982810974121</v>
+        <v>2.150530338287354</v>
       </c>
       <c r="F29" t="n">
-        <v>2.128283739089966</v>
+        <v>2.147023677825928</v>
       </c>
       <c r="G29" t="n">
-        <v>2.05635142326355</v>
+        <v>2.267749786376953</v>
       </c>
       <c r="H29" t="n">
-        <v>2.208867311477661</v>
+        <v>2.156993389129639</v>
       </c>
       <c r="I29" t="n">
-        <v>2.275316953659058</v>
+        <v>2.217350006103516</v>
       </c>
       <c r="J29" t="n">
-        <v>2.114943981170654</v>
+        <v>2.263726711273193</v>
       </c>
       <c r="K29" t="n">
-        <v>2.101926803588867</v>
+        <v>2.087183713912964</v>
       </c>
       <c r="L29" t="n">
-        <v>2.159374833106995</v>
+        <v>2.175108599662781</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.146647691726685</v>
+        <v>2.190424919128418</v>
       </c>
       <c r="C30" t="n">
-        <v>2.299957990646362</v>
+        <v>2.194404125213623</v>
       </c>
       <c r="D30" t="n">
-        <v>2.165012121200562</v>
+        <v>2.828807353973389</v>
       </c>
       <c r="E30" t="n">
-        <v>2.354154825210571</v>
+        <v>2.476188182830811</v>
       </c>
       <c r="F30" t="n">
-        <v>2.257188320159912</v>
+        <v>2.195895195007324</v>
       </c>
       <c r="G30" t="n">
-        <v>2.221490383148193</v>
+        <v>2.185436725616455</v>
       </c>
       <c r="H30" t="n">
-        <v>2.375347137451172</v>
+        <v>2.39391040802002</v>
       </c>
       <c r="I30" t="n">
-        <v>2.220329284667969</v>
+        <v>2.423827648162842</v>
       </c>
       <c r="J30" t="n">
-        <v>2.164023876190186</v>
+        <v>2.275707721710205</v>
       </c>
       <c r="K30" t="n">
-        <v>2.101545810699463</v>
+        <v>2.335537910461426</v>
       </c>
       <c r="L30" t="n">
-        <v>2.230569744110107</v>
+        <v>2.350014019012451</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1.882478952407837</v>
+        <v>1.979950189590454</v>
       </c>
       <c r="C31" t="n">
-        <v>1.896780729293823</v>
+        <v>1.988930940628052</v>
       </c>
       <c r="D31" t="n">
-        <v>1.848394632339478</v>
+        <v>1.964004755020142</v>
       </c>
       <c r="E31" t="n">
-        <v>1.92296838760376</v>
+        <v>1.872214078903198</v>
       </c>
       <c r="F31" t="n">
-        <v>2.065662145614624</v>
+        <v>1.877711057662964</v>
       </c>
       <c r="G31" t="n">
-        <v>1.881231069564819</v>
+        <v>1.926599264144897</v>
       </c>
       <c r="H31" t="n">
-        <v>1.979219913482666</v>
+        <v>1.95103907585144</v>
       </c>
       <c r="I31" t="n">
-        <v>2.007809400558472</v>
+        <v>1.898656129837036</v>
       </c>
       <c r="J31" t="n">
-        <v>2.009249925613403</v>
+        <v>1.861248254776001</v>
       </c>
       <c r="K31" t="n">
-        <v>1.830440998077393</v>
+        <v>1.902650356292725</v>
       </c>
       <c r="L31" t="n">
-        <v>1.932423615455627</v>
+        <v>1.922300410270691</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>2.03333592414856</v>
+        <v>1.937076091766357</v>
       </c>
       <c r="C32" t="n">
-        <v>2.562090635299683</v>
+        <v>2.026829481124878</v>
       </c>
       <c r="D32" t="n">
-        <v>2.061052799224854</v>
+        <v>2.005890846252441</v>
       </c>
       <c r="E32" t="n">
-        <v>2.174504518508911</v>
+        <v>2.036810159683228</v>
       </c>
       <c r="F32" t="n">
-        <v>2.057539224624634</v>
+        <v>2.105142831802368</v>
       </c>
       <c r="G32" t="n">
-        <v>2.096002817153931</v>
+        <v>2.14356255531311</v>
       </c>
       <c r="H32" t="n">
-        <v>2.063786029815674</v>
+        <v>2.168965578079224</v>
       </c>
       <c r="I32" t="n">
-        <v>2.075468063354492</v>
+        <v>1.991923093795776</v>
       </c>
       <c r="J32" t="n">
-        <v>2.236102342605591</v>
+        <v>2.060249805450439</v>
       </c>
       <c r="K32" t="n">
-        <v>2.106317281723022</v>
+        <v>1.961488485336304</v>
       </c>
       <c r="L32" t="n">
-        <v>2.146619963645935</v>
+        <v>2.043793892860413</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.129429578781128</v>
+        <v>2.186415910720825</v>
       </c>
       <c r="C33" t="n">
-        <v>2.188563585281372</v>
+        <v>2.166531801223755</v>
       </c>
       <c r="D33" t="n">
-        <v>2.290525197982788</v>
+        <v>2.153904914855957</v>
       </c>
       <c r="E33" t="n">
-        <v>2.151448488235474</v>
+        <v>2.294519662857056</v>
       </c>
       <c r="F33" t="n">
-        <v>2.278785705566406</v>
+        <v>2.301507472991943</v>
       </c>
       <c r="G33" t="n">
-        <v>2.357286930084229</v>
+        <v>2.495024919509888</v>
       </c>
       <c r="H33" t="n">
-        <v>2.185971021652222</v>
+        <v>2.36286735534668</v>
       </c>
       <c r="I33" t="n">
-        <v>2.311331748962402</v>
+        <v>2.14690375328064</v>
       </c>
       <c r="J33" t="n">
-        <v>2.10269570350647</v>
+        <v>2.206253051757812</v>
       </c>
       <c r="K33" t="n">
-        <v>2.246516466140747</v>
+        <v>2.110999345779419</v>
       </c>
       <c r="L33" t="n">
-        <v>2.224255442619324</v>
+        <v>2.242492818832397</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1.832587003707886</v>
+        <v>1.999033689498901</v>
       </c>
       <c r="C34" t="n">
-        <v>2.04755425453186</v>
+        <v>2.158016681671143</v>
       </c>
       <c r="D34" t="n">
-        <v>1.981193780899048</v>
+        <v>2.228824615478516</v>
       </c>
       <c r="E34" t="n">
-        <v>2.076242923736572</v>
+        <v>2.177948713302612</v>
       </c>
       <c r="F34" t="n">
-        <v>1.866723537445068</v>
+        <v>1.864744901657104</v>
       </c>
       <c r="G34" t="n">
-        <v>1.904499053955078</v>
+        <v>1.890685081481934</v>
       </c>
       <c r="H34" t="n">
-        <v>1.932047605514526</v>
+        <v>1.92558765411377</v>
       </c>
       <c r="I34" t="n">
-        <v>1.970904111862183</v>
+        <v>2.181440591812134</v>
       </c>
       <c r="J34" t="n">
-        <v>1.875514030456543</v>
+        <v>1.916623830795288</v>
       </c>
       <c r="K34" t="n">
-        <v>1.949995279312134</v>
+        <v>1.945981502532959</v>
       </c>
       <c r="L34" t="n">
-        <v>1.94372615814209</v>
+        <v>2.028888726234436</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.704545497894287</v>
+        <v>2.659575223922729</v>
       </c>
       <c r="C35" t="n">
-        <v>2.449144124984741</v>
+        <v>2.491039514541626</v>
       </c>
       <c r="D35" t="n">
-        <v>2.53618049621582</v>
+        <v>2.606207132339478</v>
       </c>
       <c r="E35" t="n">
-        <v>2.596015214920044</v>
+        <v>2.409719467163086</v>
       </c>
       <c r="F35" t="n">
-        <v>2.528452634811401</v>
+        <v>2.537891864776611</v>
       </c>
       <c r="G35" t="n">
-        <v>2.528176307678223</v>
+        <v>2.538406610488892</v>
       </c>
       <c r="H35" t="n">
-        <v>2.523235321044922</v>
+        <v>2.41769814491272</v>
       </c>
       <c r="I35" t="n">
-        <v>2.430878877639771</v>
+        <v>2.596237421035767</v>
       </c>
       <c r="J35" t="n">
-        <v>2.504379034042358</v>
+        <v>2.749531030654907</v>
       </c>
       <c r="K35" t="n">
-        <v>2.391770124435425</v>
+        <v>2.633166790008545</v>
       </c>
       <c r="L35" t="n">
-        <v>2.519277763366699</v>
+        <v>2.563947319984436</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1.905349016189575</v>
+        <v>2.070228576660156</v>
       </c>
       <c r="C36" t="n">
-        <v>1.981498956680298</v>
+        <v>2.181705236434937</v>
       </c>
       <c r="D36" t="n">
-        <v>2.006765365600586</v>
+        <v>2.155883550643921</v>
       </c>
       <c r="E36" t="n">
-        <v>2.245100736618042</v>
+        <v>2.202260494232178</v>
       </c>
       <c r="F36" t="n">
-        <v>1.903015613555908</v>
+        <v>2.105138540267944</v>
       </c>
       <c r="G36" t="n">
-        <v>1.954190969467163</v>
+        <v>2.036841869354248</v>
       </c>
       <c r="H36" t="n">
-        <v>1.791335821151733</v>
+        <v>2.187450647354126</v>
       </c>
       <c r="I36" t="n">
-        <v>2.060129165649414</v>
+        <v>2.043303728103638</v>
       </c>
       <c r="J36" t="n">
-        <v>1.935487747192383</v>
+        <v>2.22234582901001</v>
       </c>
       <c r="K36" t="n">
-        <v>2.00342869758606</v>
+        <v>2.047784805297852</v>
       </c>
       <c r="L36" t="n">
-        <v>1.978630208969116</v>
+        <v>2.125294327735901</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.197147369384766</v>
+        <v>2.33655834197998</v>
       </c>
       <c r="C37" t="n">
-        <v>2.248425722122192</v>
+        <v>2.500137567520142</v>
       </c>
       <c r="D37" t="n">
-        <v>2.110022306442261</v>
+        <v>2.272708177566528</v>
       </c>
       <c r="E37" t="n">
-        <v>2.304958581924438</v>
+        <v>2.585946321487427</v>
       </c>
       <c r="F37" t="n">
-        <v>2.290842294692993</v>
+        <v>2.344075202941895</v>
       </c>
       <c r="G37" t="n">
-        <v>2.249542713165283</v>
+        <v>2.192085027694702</v>
       </c>
       <c r="H37" t="n">
-        <v>2.60703182220459</v>
+        <v>2.491641998291016</v>
       </c>
       <c r="I37" t="n">
-        <v>2.09997034072876</v>
+        <v>2.486193180084229</v>
       </c>
       <c r="J37" t="n">
-        <v>2.263601303100586</v>
+        <v>2.396925449371338</v>
       </c>
       <c r="K37" t="n">
-        <v>2.149636268615723</v>
+        <v>2.193443059921265</v>
       </c>
       <c r="L37" t="n">
-        <v>2.252117872238159</v>
+        <v>2.379971432685852</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2.557813882827759</v>
+        <v>2.282696962356567</v>
       </c>
       <c r="C38" t="n">
-        <v>2.634510278701782</v>
+        <v>2.655236721038818</v>
       </c>
       <c r="D38" t="n">
-        <v>2.518897771835327</v>
+        <v>2.438332319259644</v>
       </c>
       <c r="E38" t="n">
-        <v>2.733924627304077</v>
+        <v>2.561967134475708</v>
       </c>
       <c r="F38" t="n">
-        <v>2.77854061126709</v>
+        <v>2.323571443557739</v>
       </c>
       <c r="G38" t="n">
-        <v>2.664227724075317</v>
+        <v>2.483770370483398</v>
       </c>
       <c r="H38" t="n">
-        <v>2.490985155105591</v>
+        <v>2.596386671066284</v>
       </c>
       <c r="I38" t="n">
-        <v>2.632489442825317</v>
+        <v>2.621984720230103</v>
       </c>
       <c r="J38" t="n">
-        <v>2.611937046051025</v>
+        <v>2.605777263641357</v>
       </c>
       <c r="K38" t="n">
-        <v>2.631660461425781</v>
+        <v>2.752874374389648</v>
       </c>
       <c r="L38" t="n">
-        <v>2.625498700141907</v>
+        <v>2.532259798049927</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.330228805541992</v>
+        <v>2.271612882614136</v>
       </c>
       <c r="C39" t="n">
-        <v>2.31597375869751</v>
+        <v>2.387798547744751</v>
       </c>
       <c r="D39" t="n">
-        <v>2.167381763458252</v>
+        <v>2.320477485656738</v>
       </c>
       <c r="E39" t="n">
-        <v>2.493024587631226</v>
+        <v>2.243165254592896</v>
       </c>
       <c r="F39" t="n">
-        <v>2.168937921524048</v>
+        <v>2.28858494758606</v>
       </c>
       <c r="G39" t="n">
-        <v>2.305041313171387</v>
+        <v>2.343412399291992</v>
       </c>
       <c r="H39" t="n">
-        <v>2.223395347595215</v>
+        <v>2.389787197113037</v>
       </c>
       <c r="I39" t="n">
-        <v>2.364708185195923</v>
+        <v>2.236690759658813</v>
       </c>
       <c r="J39" t="n">
-        <v>2.21073055267334</v>
+        <v>2.400642156600952</v>
       </c>
       <c r="K39" t="n">
-        <v>2.108267068862915</v>
+        <v>2.203412055969238</v>
       </c>
       <c r="L39" t="n">
-        <v>2.268768930435181</v>
+        <v>2.308558368682861</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.310281991958618</v>
+        <v>2.30761981010437</v>
       </c>
       <c r="C40" t="n">
-        <v>2.295907258987427</v>
+        <v>2.170971393585205</v>
       </c>
       <c r="D40" t="n">
-        <v>2.033488750457764</v>
+        <v>2.161510944366455</v>
       </c>
       <c r="E40" t="n">
-        <v>2.159847974777222</v>
+        <v>2.280701160430908</v>
       </c>
       <c r="F40" t="n">
-        <v>2.0779869556427</v>
+        <v>2.12609076499939</v>
       </c>
       <c r="G40" t="n">
-        <v>2.140495300292969</v>
+        <v>2.099154949188232</v>
       </c>
       <c r="H40" t="n">
-        <v>2.109330892562866</v>
+        <v>2.128066539764404</v>
       </c>
       <c r="I40" t="n">
-        <v>2.119871616363525</v>
+        <v>2.130057334899902</v>
       </c>
       <c r="J40" t="n">
-        <v>2.037934303283691</v>
+        <v>2.215379238128662</v>
       </c>
       <c r="K40" t="n">
-        <v>2.174351215362549</v>
+        <v>2.101037740707397</v>
       </c>
       <c r="L40" t="n">
-        <v>2.145949625968933</v>
+        <v>2.172058987617492</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.25438117980957</v>
+        <v>2.347392320632935</v>
       </c>
       <c r="C41" t="n">
-        <v>2.348072290420532</v>
+        <v>2.589284420013428</v>
       </c>
       <c r="D41" t="n">
-        <v>2.371702909469604</v>
+        <v>2.419705629348755</v>
       </c>
       <c r="E41" t="n">
-        <v>2.21076774597168</v>
+        <v>2.81782603263855</v>
       </c>
       <c r="F41" t="n">
-        <v>2.380730867385864</v>
+        <v>2.435174703598022</v>
       </c>
       <c r="G41" t="n">
-        <v>2.352977275848389</v>
+        <v>2.422683477401733</v>
       </c>
       <c r="H41" t="n">
-        <v>2.311047315597534</v>
+        <v>2.294530391693115</v>
       </c>
       <c r="I41" t="n">
-        <v>2.372121095657349</v>
+        <v>2.553282976150513</v>
       </c>
       <c r="J41" t="n">
-        <v>2.197532653808594</v>
+        <v>2.342034101486206</v>
       </c>
       <c r="K41" t="n">
-        <v>2.360780477523804</v>
+        <v>2.334548234939575</v>
       </c>
       <c r="L41" t="n">
-        <v>2.316011381149292</v>
+        <v>2.455646228790283</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1.906165599822998</v>
+        <v>2.068239688873291</v>
       </c>
       <c r="C42" t="n">
-        <v>2.215582609176636</v>
+        <v>2.101171493530273</v>
       </c>
       <c r="D42" t="n">
-        <v>2.482969760894775</v>
+        <v>1.982438564300537</v>
       </c>
       <c r="E42" t="n">
-        <v>1.970964908599854</v>
+        <v>2.083258628845215</v>
       </c>
       <c r="F42" t="n">
-        <v>2.04546070098877</v>
+        <v>2.161391973495483</v>
       </c>
       <c r="G42" t="n">
-        <v>2.067838430404663</v>
+        <v>2.022736310958862</v>
       </c>
       <c r="H42" t="n">
-        <v>2.012729406356812</v>
+        <v>1.996820211410522</v>
       </c>
       <c r="I42" t="n">
-        <v>1.992876529693604</v>
+        <v>1.992824554443359</v>
       </c>
       <c r="J42" t="n">
-        <v>2.336572170257568</v>
+        <v>2.08057713508606</v>
       </c>
       <c r="K42" t="n">
-        <v>1.95418643951416</v>
+        <v>2.05415940284729</v>
       </c>
       <c r="L42" t="n">
-        <v>2.098534655570984</v>
+        <v>2.054361796379089</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.12811541557312</v>
+        <v>2.417708873748779</v>
       </c>
       <c r="C43" t="n">
-        <v>2.186447143554688</v>
+        <v>2.19031810760498</v>
       </c>
       <c r="D43" t="n">
-        <v>2.218563795089722</v>
+        <v>2.204280376434326</v>
       </c>
       <c r="E43" t="n">
-        <v>2.234847068786621</v>
+        <v>2.185303688049316</v>
       </c>
       <c r="F43" t="n">
-        <v>2.224445104598999</v>
+        <v>2.184233665466309</v>
       </c>
       <c r="G43" t="n">
-        <v>2.29460072517395</v>
+        <v>2.27918553352356</v>
       </c>
       <c r="H43" t="n">
-        <v>2.225386381149292</v>
+        <v>2.210368633270264</v>
       </c>
       <c r="I43" t="n">
-        <v>2.150906085968018</v>
+        <v>2.157987356185913</v>
       </c>
       <c r="J43" t="n">
-        <v>2.083571195602417</v>
+        <v>2.266750574111938</v>
       </c>
       <c r="K43" t="n">
-        <v>2.123507261276245</v>
+        <v>2.141067981719971</v>
       </c>
       <c r="L43" t="n">
-        <v>2.187039017677307</v>
+        <v>2.223720479011535</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>2.171854019165039</v>
+        <v>2.41922664642334</v>
       </c>
       <c r="C44" t="n">
-        <v>2.105794668197632</v>
+        <v>2.249672889709473</v>
       </c>
       <c r="D44" t="n">
-        <v>2.256575584411621</v>
+        <v>2.254147291183472</v>
       </c>
       <c r="E44" t="n">
-        <v>2.105366230010986</v>
+        <v>2.160369157791138</v>
       </c>
       <c r="F44" t="n">
-        <v>2.193802833557129</v>
+        <v>2.353367328643799</v>
       </c>
       <c r="G44" t="n">
-        <v>2.087336778640747</v>
+        <v>2.263116598129272</v>
       </c>
       <c r="H44" t="n">
-        <v>2.165121793746948</v>
+        <v>2.163719654083252</v>
       </c>
       <c r="I44" t="n">
-        <v>2.202985048294067</v>
+        <v>2.186855316162109</v>
       </c>
       <c r="J44" t="n">
-        <v>2.060333967208862</v>
+        <v>2.190296173095703</v>
       </c>
       <c r="K44" t="n">
-        <v>2.275416612625122</v>
+        <v>2.392784595489502</v>
       </c>
       <c r="L44" t="n">
-        <v>2.162458753585816</v>
+        <v>2.263355565071106</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1.905023336410522</v>
+        <v>2.021770000457764</v>
       </c>
       <c r="C45" t="n">
-        <v>2.165253400802612</v>
+        <v>2.006764888763428</v>
       </c>
       <c r="D45" t="n">
-        <v>1.824291467666626</v>
+        <v>1.948423147201538</v>
       </c>
       <c r="E45" t="n">
-        <v>1.960995197296143</v>
+        <v>1.90354323387146</v>
       </c>
       <c r="F45" t="n">
-        <v>1.969972610473633</v>
+        <v>1.96987247467041</v>
       </c>
       <c r="G45" t="n">
-        <v>2.062674760818481</v>
+        <v>2.011764287948608</v>
       </c>
       <c r="H45" t="n">
-        <v>2.185688257217407</v>
+        <v>1.951422691345215</v>
       </c>
       <c r="I45" t="n">
-        <v>1.947968006134033</v>
+        <v>1.917015314102173</v>
       </c>
       <c r="J45" t="n">
-        <v>1.856311559677124</v>
+        <v>2.086567878723145</v>
       </c>
       <c r="K45" t="n">
-        <v>2.098525285720825</v>
+        <v>2.017257690429688</v>
       </c>
       <c r="L45" t="n">
-        <v>1.997670388221741</v>
+        <v>1.983440160751343</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1.821138143539429</v>
+        <v>1.812288045883179</v>
       </c>
       <c r="C46" t="n">
-        <v>1.895377159118652</v>
+        <v>1.887562990188599</v>
       </c>
       <c r="D46" t="n">
-        <v>1.823319673538208</v>
+        <v>1.837828159332275</v>
       </c>
       <c r="E46" t="n">
-        <v>1.835518598556519</v>
+        <v>1.840314388275146</v>
       </c>
       <c r="F46" t="n">
-        <v>1.986814498901367</v>
+        <v>1.783257961273193</v>
       </c>
       <c r="G46" t="n">
-        <v>2.049733638763428</v>
+        <v>1.97635817527771</v>
       </c>
       <c r="H46" t="n">
-        <v>1.7923903465271</v>
+        <v>1.858152866363525</v>
       </c>
       <c r="I46" t="n">
-        <v>1.949700355529785</v>
+        <v>1.909531831741333</v>
       </c>
       <c r="J46" t="n">
-        <v>1.888694286346436</v>
+        <v>1.892578125</v>
       </c>
       <c r="K46" t="n">
-        <v>2.024849414825439</v>
+        <v>2.050675630569458</v>
       </c>
       <c r="L46" t="n">
-        <v>1.906753611564636</v>
+        <v>1.884854817390442</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.572418451309204</v>
+        <v>2.658577919006348</v>
       </c>
       <c r="C47" t="n">
-        <v>2.925679445266724</v>
+        <v>2.590262651443481</v>
       </c>
       <c r="D47" t="n">
-        <v>2.601696014404297</v>
+        <v>2.486036062240601</v>
       </c>
       <c r="E47" t="n">
-        <v>2.686781644821167</v>
+        <v>2.684008121490479</v>
       </c>
       <c r="F47" t="n">
-        <v>2.68060827255249</v>
+        <v>2.556354761123657</v>
       </c>
       <c r="G47" t="n">
-        <v>2.653017997741699</v>
+        <v>2.514966726303101</v>
       </c>
       <c r="H47" t="n">
-        <v>2.630861282348633</v>
+        <v>2.538594961166382</v>
       </c>
       <c r="I47" t="n">
-        <v>2.494077920913696</v>
+        <v>2.600249528884888</v>
       </c>
       <c r="J47" t="n">
-        <v>2.655844688415527</v>
+        <v>2.807697057723999</v>
       </c>
       <c r="K47" t="n">
-        <v>2.72510814666748</v>
+        <v>2.583277225494385</v>
       </c>
       <c r="L47" t="n">
-        <v>2.662609386444092</v>
+        <v>2.602002501487732</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.330945730209351</v>
+        <v>2.168349027633667</v>
       </c>
       <c r="C48" t="n">
-        <v>2.339164018630981</v>
+        <v>2.232186794281006</v>
       </c>
       <c r="D48" t="n">
-        <v>2.432380676269531</v>
+        <v>2.291550636291504</v>
       </c>
       <c r="E48" t="n">
-        <v>2.323297262191772</v>
+        <v>2.179329872131348</v>
       </c>
       <c r="F48" t="n">
-        <v>2.295257091522217</v>
+        <v>2.297527074813843</v>
       </c>
       <c r="G48" t="n">
-        <v>2.247371673583984</v>
+        <v>2.203260183334351</v>
       </c>
       <c r="H48" t="n">
-        <v>2.184731245040894</v>
+        <v>2.184876203536987</v>
       </c>
       <c r="I48" t="n">
-        <v>2.318336009979248</v>
+        <v>2.243661642074585</v>
       </c>
       <c r="J48" t="n">
-        <v>2.192113637924194</v>
+        <v>2.213233709335327</v>
       </c>
       <c r="K48" t="n">
-        <v>2.508705377578735</v>
+        <v>2.27159309387207</v>
       </c>
       <c r="L48" t="n">
-        <v>2.317230272293091</v>
+        <v>2.228556823730469</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.418093681335449</v>
+        <v>2.284050941467285</v>
       </c>
       <c r="C49" t="n">
-        <v>2.4263596534729</v>
+        <v>2.388803005218506</v>
       </c>
       <c r="D49" t="n">
-        <v>2.593574523925781</v>
+        <v>2.424688816070557</v>
       </c>
       <c r="E49" t="n">
-        <v>2.188555240631104</v>
+        <v>2.451752662658691</v>
       </c>
       <c r="F49" t="n">
-        <v>2.497455835342407</v>
+        <v>2.630348443984985</v>
       </c>
       <c r="G49" t="n">
-        <v>2.65540337562561</v>
+        <v>2.393966436386108</v>
       </c>
       <c r="H49" t="n">
-        <v>2.517150640487671</v>
+        <v>2.53404712677002</v>
       </c>
       <c r="I49" t="n">
-        <v>2.307872772216797</v>
+        <v>2.52773642539978</v>
       </c>
       <c r="J49" t="n">
-        <v>2.444570064544678</v>
+        <v>2.281765937805176</v>
       </c>
       <c r="K49" t="n">
-        <v>2.32293963432312</v>
+        <v>2.371599197387695</v>
       </c>
       <c r="L49" t="n">
-        <v>2.437197542190552</v>
+        <v>2.42887589931488</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>2.335761308670044</v>
+        <v>2.369387865066528</v>
       </c>
       <c r="C50" t="n">
-        <v>2.060238122940063</v>
+        <v>2.397983551025391</v>
       </c>
       <c r="D50" t="n">
-        <v>2.18322229385376</v>
+        <v>2.368027925491333</v>
       </c>
       <c r="E50" t="n">
-        <v>2.02785849571228</v>
+        <v>2.117112398147583</v>
       </c>
       <c r="F50" t="n">
-        <v>2.173141241073608</v>
+        <v>2.252260208129883</v>
       </c>
       <c r="G50" t="n">
-        <v>2.188623905181885</v>
+        <v>2.258775472640991</v>
       </c>
       <c r="H50" t="n">
-        <v>2.072998523712158</v>
+        <v>2.191080570220947</v>
       </c>
       <c r="I50" t="n">
-        <v>2.102301359176636</v>
+        <v>2.20327615737915</v>
       </c>
       <c r="J50" t="n">
-        <v>2.172899484634399</v>
+        <v>2.352420806884766</v>
       </c>
       <c r="K50" t="n">
-        <v>2.24969744682312</v>
+        <v>2.257642507553101</v>
       </c>
       <c r="L50" t="n">
-        <v>2.156674218177796</v>
+        <v>2.276796746253967</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1.952964544296265</v>
+        <v>2.284588813781738</v>
       </c>
       <c r="C51" t="n">
-        <v>2.090547800064087</v>
+        <v>2.789334774017334</v>
       </c>
       <c r="D51" t="n">
-        <v>1.886650085449219</v>
+        <v>2.304543972015381</v>
       </c>
       <c r="E51" t="n">
-        <v>2.161344766616821</v>
+        <v>2.347907066345215</v>
       </c>
       <c r="F51" t="n">
-        <v>2.087997674942017</v>
+        <v>2.202279806137085</v>
       </c>
       <c r="G51" t="n">
-        <v>1.930941343307495</v>
+        <v>2.293549537658691</v>
       </c>
       <c r="H51" t="n">
-        <v>1.894911050796509</v>
+        <v>2.406966924667358</v>
       </c>
       <c r="I51" t="n">
-        <v>2.038323640823364</v>
+        <v>2.223395347595215</v>
       </c>
       <c r="J51" t="n">
-        <v>2.076226711273193</v>
+        <v>2.343646049499512</v>
       </c>
       <c r="K51" t="n">
-        <v>2.012377738952637</v>
+        <v>2.426364183425903</v>
       </c>
       <c r="L51" t="n">
-        <v>2.013228535652161</v>
+        <v>2.362257647514343</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.269472436904907</v>
+        <v>2.264002814292908</v>
       </c>
       <c r="C52" t="n">
-        <v>2.29900354385376</v>
+        <v>2.332594714164734</v>
       </c>
       <c r="D52" t="n">
-        <v>2.248725748062134</v>
+        <v>2.259169912338257</v>
       </c>
       <c r="E52" t="n">
-        <v>2.31498016834259</v>
+        <v>2.284176559448242</v>
       </c>
       <c r="F52" t="n">
-        <v>2.244920988082886</v>
+        <v>2.270351638793946</v>
       </c>
       <c r="G52" t="n">
-        <v>2.285616345405578</v>
+        <v>2.254747338294983</v>
       </c>
       <c r="H52" t="n">
-        <v>2.257509775161743</v>
+        <v>2.249609227180481</v>
       </c>
       <c r="I52" t="n">
-        <v>2.233497200012207</v>
+        <v>2.262070341110229</v>
       </c>
       <c r="J52" t="n">
-        <v>2.237447972297669</v>
+        <v>2.27248291015625</v>
       </c>
       <c r="K52" t="n">
-        <v>2.267731127738953</v>
+        <v>2.279721488952637</v>
       </c>
       <c r="L52" t="n">
-        <v>2.265890530586242</v>
+        <v>2.272892694473267</v>
       </c>
     </row>
   </sheetData>
